--- a/ssp_modeling/cost-benefits/cb_config_files/cb_config_params.xlsx
+++ b/ssp_modeling/cost-benefits/cb_config_files/cb_config_params.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_libya/ssp_modeling/cost-benefits/cb_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12363F61-856C-6448-B4FE-B554CB89B9E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{878647A1-ADB5-DE46-B321-6573B7CEEBE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-51200" yWindow="-7160" windowWidth="25600" windowHeight="28200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="-620" windowWidth="38400" windowHeight="21000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tx_table" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4783" uniqueCount="2057">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4783" uniqueCount="2058">
   <si>
     <t>output_variable_name</t>
   </si>
@@ -6251,6 +6251,9 @@
   </si>
   <si>
     <t>$400/tbiogas</t>
+  </si>
+  <si>
+    <t>cb:entc:technical_saving:electricity:opex</t>
   </si>
 </sst>
 </file>
@@ -6260,7 +6263,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000000000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6290,8 +6293,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6346,6 +6357,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -6378,7 +6395,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -6392,8 +6409,11 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -16866,7 +16886,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -19488,40 +19508,40 @@
       </c>
     </row>
     <row r="70" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
-        <v>13</v>
-      </c>
-      <c r="B70" t="s">
+      <c r="A70" s="12" t="s">
+        <v>2057</v>
+      </c>
+      <c r="B70" s="12" t="s">
         <v>452</v>
       </c>
-      <c r="C70">
-        <v>-1000000</v>
-      </c>
-      <c r="D70" t="s">
+      <c r="C70" s="12">
+        <v>1000000</v>
+      </c>
+      <c r="D70" s="12" t="s">
         <v>350</v>
       </c>
-      <c r="E70">
-        <v>1</v>
-      </c>
-      <c r="F70" t="s">
+      <c r="E70" s="12">
+        <v>1</v>
+      </c>
+      <c r="F70" s="12" t="s">
         <v>219</v>
       </c>
-      <c r="G70" t="b">
-        <v>1</v>
-      </c>
-      <c r="H70" t="s">
+      <c r="G70" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H70" s="12" t="s">
         <v>350</v>
       </c>
-      <c r="I70" t="s">
+      <c r="I70" s="12" t="s">
         <v>380</v>
       </c>
-      <c r="J70" t="s">
+      <c r="J70" s="12" t="s">
         <v>351</v>
       </c>
-      <c r="K70" t="s">
+      <c r="K70" s="12" t="s">
         <v>688</v>
       </c>
-      <c r="L70" t="s">
+      <c r="L70" s="12" t="s">
         <v>691</v>
       </c>
     </row>
@@ -21311,155 +21331,155 @@
         <v>703</v>
       </c>
     </row>
-    <row r="118" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="11" t="s">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
         <v>70</v>
       </c>
-      <c r="B118" s="11" t="s">
+      <c r="B118" t="s">
         <v>508</v>
       </c>
-      <c r="C118" s="11">
+      <c r="C118">
         <v>-5.2</v>
       </c>
-      <c r="D118" s="11" t="s">
+      <c r="D118" t="s">
         <v>595</v>
       </c>
-      <c r="E118" s="11">
-        <v>1</v>
-      </c>
-      <c r="F118" s="11" t="s">
+      <c r="E118">
+        <v>1</v>
+      </c>
+      <c r="F118" t="s">
         <v>275</v>
       </c>
-      <c r="G118" s="11" t="b">
+      <c r="G118" t="b">
         <v>0</v>
       </c>
-      <c r="H118" s="11" t="s">
+      <c r="H118" t="s">
         <v>646</v>
       </c>
-      <c r="I118" s="11" t="s">
+      <c r="I118" t="s">
         <v>681</v>
       </c>
-      <c r="J118" s="11" t="s">
+      <c r="J118" t="s">
         <v>351</v>
       </c>
-      <c r="K118" s="11" t="s">
+      <c r="K118" t="s">
         <v>688</v>
       </c>
-      <c r="L118" s="11" t="s">
+      <c r="L118" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="119" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="11" t="s">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
         <v>71</v>
       </c>
-      <c r="B119" s="11" t="s">
+      <c r="B119" t="s">
         <v>509</v>
       </c>
-      <c r="C119" s="11">
+      <c r="C119">
         <v>-14</v>
       </c>
-      <c r="D119" s="11" t="s">
+      <c r="D119" t="s">
         <v>595</v>
       </c>
-      <c r="E119" s="11">
-        <v>1</v>
-      </c>
-      <c r="F119" s="11" t="s">
+      <c r="E119">
+        <v>1</v>
+      </c>
+      <c r="F119" t="s">
         <v>276</v>
       </c>
-      <c r="G119" s="11" t="b">
+      <c r="G119" t="b">
         <v>0</v>
       </c>
-      <c r="H119" s="11" t="s">
+      <c r="H119" t="s">
         <v>647</v>
       </c>
-      <c r="I119" s="11" t="s">
+      <c r="I119" t="s">
         <v>681</v>
       </c>
-      <c r="J119" s="11" t="s">
+      <c r="J119" t="s">
         <v>351</v>
       </c>
-      <c r="K119" s="11" t="s">
+      <c r="K119" t="s">
         <v>688</v>
       </c>
-      <c r="L119" s="11" t="s">
+      <c r="L119" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="120" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="11" t="s">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
         <v>72</v>
       </c>
-      <c r="B120" s="11" t="s">
+      <c r="B120" t="s">
         <v>510</v>
       </c>
-      <c r="C120" s="11">
+      <c r="C120">
         <v>-5.2</v>
       </c>
-      <c r="D120" s="11" t="s">
+      <c r="D120" t="s">
         <v>595</v>
       </c>
-      <c r="E120" s="11">
-        <v>1</v>
-      </c>
-      <c r="F120" s="11" t="s">
+      <c r="E120">
+        <v>1</v>
+      </c>
+      <c r="F120" t="s">
         <v>277</v>
       </c>
-      <c r="G120" s="11" t="b">
+      <c r="G120" t="b">
         <v>0</v>
       </c>
-      <c r="H120" s="11" t="s">
+      <c r="H120" t="s">
         <v>648</v>
       </c>
-      <c r="I120" s="11" t="s">
+      <c r="I120" t="s">
         <v>681</v>
       </c>
-      <c r="J120" s="11" t="s">
+      <c r="J120" t="s">
         <v>351</v>
       </c>
-      <c r="K120" s="11" t="s">
+      <c r="K120" t="s">
         <v>688</v>
       </c>
-      <c r="L120" s="11" t="s">
+      <c r="L120" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="121" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="11" t="s">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
         <v>73</v>
       </c>
-      <c r="B121" s="11" t="s">
+      <c r="B121" t="s">
         <v>511</v>
       </c>
-      <c r="C121" s="11">
+      <c r="C121">
         <v>-0.17</v>
       </c>
-      <c r="D121" s="11" t="s">
+      <c r="D121" t="s">
         <v>595</v>
       </c>
-      <c r="E121" s="11">
-        <v>1</v>
-      </c>
-      <c r="F121" s="11" t="s">
+      <c r="E121">
+        <v>1</v>
+      </c>
+      <c r="F121" t="s">
         <v>278</v>
       </c>
-      <c r="G121" s="11" t="b">
+      <c r="G121" t="b">
         <v>0</v>
       </c>
-      <c r="H121" s="11" t="s">
+      <c r="H121" t="s">
         <v>649</v>
       </c>
-      <c r="I121" s="11" t="s">
+      <c r="I121" t="s">
         <v>681</v>
       </c>
-      <c r="J121" s="11" t="s">
+      <c r="J121" t="s">
         <v>351</v>
       </c>
-      <c r="K121" s="11" t="s">
+      <c r="K121" t="s">
         <v>688</v>
       </c>
-      <c r="L121" s="11" t="s">
+      <c r="L121" t="s">
         <v>703</v>
       </c>
     </row>
@@ -22794,13 +22814,13 @@
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A157" s="12" t="s">
+      <c r="A157" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="B157" s="12" t="s">
+      <c r="B157" s="11" t="s">
         <v>518</v>
       </c>
-      <c r="C157" s="12">
+      <c r="C157" s="11">
         <f>-500/3</f>
         <v>-166.66666666666666</v>
       </c>
@@ -22833,13 +22853,13 @@
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A158" s="12" t="s">
+      <c r="A158" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="B158" s="12" t="s">
+      <c r="B158" s="11" t="s">
         <v>517</v>
       </c>
-      <c r="C158" s="12">
+      <c r="C158" s="11">
         <f>-170/3</f>
         <v>-56.666666666666664</v>
       </c>
@@ -22872,13 +22892,13 @@
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A159" s="12" t="s">
+      <c r="A159" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="B159" s="12" t="s">
+      <c r="B159" s="11" t="s">
         <v>519</v>
       </c>
-      <c r="C159" s="12">
+      <c r="C159" s="11">
         <f>-500/3</f>
         <v>-166.66666666666666</v>
       </c>

--- a/ssp_modeling/cost-benefits/cb_config_files/cb_config_params.xlsx
+++ b/ssp_modeling/cost-benefits/cb_config_files/cb_config_params.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_libya/ssp_modeling/cost-benefits/cb_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{774E7CAE-8D20-5440-B586-440310A79CCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DFB0F81-4B49-3C40-BA96-CCBA4A139C98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-51200" yWindow="-7160" windowWidth="25600" windowHeight="28200" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-39500" yWindow="-7160" windowWidth="31780" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tx_table" sheetId="1" r:id="rId1"/>
@@ -6710,7 +6710,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:E213"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -6757,7 +6756,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>46</v>
       </c>
@@ -6774,7 +6773,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>47</v>
       </c>
@@ -6791,7 +6790,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>48</v>
       </c>
@@ -6808,7 +6807,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>49</v>
       </c>
@@ -6825,7 +6824,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>50</v>
       </c>
@@ -6842,7 +6841,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>51</v>
       </c>
@@ -6859,7 +6858,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>52</v>
       </c>
@@ -6876,7 +6875,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>53</v>
       </c>
@@ -6893,7 +6892,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>54</v>
       </c>
@@ -6910,7 +6909,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>55</v>
       </c>
@@ -6927,7 +6926,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>56</v>
       </c>
@@ -6944,7 +6943,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>57</v>
       </c>
@@ -6961,7 +6960,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>58</v>
       </c>
@@ -6978,7 +6977,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>200</v>
       </c>
@@ -6995,7 +6994,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>198</v>
       </c>
@@ -7012,7 +7011,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>197</v>
       </c>
@@ -7063,7 +7062,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>76</v>
       </c>
@@ -7080,7 +7079,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>61</v>
       </c>
@@ -7097,7 +7096,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>195</v>
       </c>
@@ -7114,7 +7113,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>116</v>
       </c>
@@ -7131,7 +7130,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>117</v>
       </c>
@@ -7148,7 +7147,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>118</v>
       </c>
@@ -7165,7 +7164,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>119</v>
       </c>
@@ -7182,7 +7181,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>120</v>
       </c>
@@ -7199,7 +7198,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>121</v>
       </c>
@@ -7216,7 +7215,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>122</v>
       </c>
@@ -7233,7 +7232,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>123</v>
       </c>
@@ -7250,7 +7249,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>124</v>
       </c>
@@ -7267,7 +7266,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>125</v>
       </c>
@@ -7284,7 +7283,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>126</v>
       </c>
@@ -7301,7 +7300,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>127</v>
       </c>
@@ -7318,7 +7317,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>128</v>
       </c>
@@ -7335,7 +7334,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>129</v>
       </c>
@@ -7352,7 +7351,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>130</v>
       </c>
@@ -7369,7 +7368,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>131</v>
       </c>
@@ -7386,7 +7385,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>132</v>
       </c>
@@ -7403,7 +7402,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>133</v>
       </c>
@@ -7420,7 +7419,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>134</v>
       </c>
@@ -7437,7 +7436,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>135</v>
       </c>
@@ -7454,7 +7453,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>136</v>
       </c>
@@ -7471,7 +7470,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>137</v>
       </c>
@@ -7488,7 +7487,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>138</v>
       </c>
@@ -7505,7 +7504,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>139</v>
       </c>
@@ -7522,7 +7521,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>140</v>
       </c>
@@ -7539,7 +7538,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>141</v>
       </c>
@@ -7556,7 +7555,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>142</v>
       </c>
@@ -7573,7 +7572,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>143</v>
       </c>
@@ -7590,7 +7589,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>144</v>
       </c>
@@ -7607,7 +7606,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>145</v>
       </c>
@@ -7624,7 +7623,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>146</v>
       </c>
@@ -7641,7 +7640,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>147</v>
       </c>
@@ -7658,7 +7657,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>148</v>
       </c>
@@ -7675,7 +7674,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>149</v>
       </c>
@@ -7692,7 +7691,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>150</v>
       </c>
@@ -7709,7 +7708,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>151</v>
       </c>
@@ -7726,7 +7725,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>152</v>
       </c>
@@ -7743,7 +7742,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>153</v>
       </c>
@@ -7760,7 +7759,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>154</v>
       </c>
@@ -7777,7 +7776,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>155</v>
       </c>
@@ -7794,7 +7793,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>156</v>
       </c>
@@ -7811,7 +7810,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>157</v>
       </c>
@@ -7828,7 +7827,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>158</v>
       </c>
@@ -7845,7 +7844,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>159</v>
       </c>
@@ -7862,7 +7861,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>160</v>
       </c>
@@ -7879,7 +7878,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>161</v>
       </c>
@@ -7896,7 +7895,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>162</v>
       </c>
@@ -7913,7 +7912,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>106</v>
       </c>
@@ -7930,7 +7929,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>87</v>
       </c>
@@ -7947,7 +7946,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>85</v>
       </c>
@@ -7964,7 +7963,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>86</v>
       </c>
@@ -7981,7 +7980,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>64</v>
       </c>
@@ -7998,7 +7997,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>12</v>
       </c>
@@ -8032,7 +8031,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>13</v>
       </c>
@@ -8049,7 +8048,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>185</v>
       </c>
@@ -8066,7 +8065,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>191</v>
       </c>
@@ -8083,7 +8082,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>192</v>
       </c>
@@ -8100,7 +8099,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>102</v>
       </c>
@@ -8117,7 +8116,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>103</v>
       </c>
@@ -8134,7 +8133,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>104</v>
       </c>
@@ -8151,7 +8150,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>100</v>
       </c>
@@ -8168,7 +8167,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>101</v>
       </c>
@@ -8185,7 +8184,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>105</v>
       </c>
@@ -8202,7 +8201,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>77</v>
       </c>
@@ -8219,7 +8218,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>62</v>
       </c>
@@ -8236,7 +8235,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>169</v>
       </c>
@@ -8253,7 +8252,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>167</v>
       </c>
@@ -8270,7 +8269,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>165</v>
       </c>
@@ -8287,7 +8286,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>163</v>
       </c>
@@ -8355,7 +8354,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>66</v>
       </c>
@@ -8372,7 +8371,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>74</v>
       </c>
@@ -8389,7 +8388,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>75</v>
       </c>
@@ -8406,7 +8405,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>188</v>
       </c>
@@ -8423,7 +8422,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>187</v>
       </c>
@@ -8440,7 +8439,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>190</v>
       </c>
@@ -8457,7 +8456,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>189</v>
       </c>
@@ -8474,7 +8473,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>186</v>
       </c>
@@ -8491,7 +8490,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A105" s="5" t="s">
         <v>2037</v>
       </c>
@@ -8508,7 +8507,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>207</v>
       </c>
@@ -8525,7 +8524,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>18</v>
       </c>
@@ -8542,7 +8541,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>19</v>
       </c>
@@ -8559,7 +8558,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>206</v>
       </c>
@@ -8576,7 +8575,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>204</v>
       </c>
@@ -8593,7 +8592,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>205</v>
       </c>
@@ -8610,7 +8609,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>115</v>
       </c>
@@ -8627,7 +8626,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113" s="6" t="s">
         <v>2044</v>
       </c>
@@ -8641,7 +8640,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A114" s="5" t="s">
         <v>2038</v>
       </c>
@@ -8658,7 +8657,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A115" s="5" t="s">
         <v>2042</v>
       </c>
@@ -8675,7 +8674,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A116" s="5" t="s">
         <v>2040</v>
       </c>
@@ -8692,7 +8691,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>37</v>
       </c>
@@ -8709,7 +8708,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>38</v>
       </c>
@@ -8726,7 +8725,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>39</v>
       </c>
@@ -8743,7 +8742,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>40</v>
       </c>
@@ -8760,7 +8759,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>41</v>
       </c>
@@ -8777,7 +8776,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>42</v>
       </c>
@@ -8794,7 +8793,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="123" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>43</v>
       </c>
@@ -8811,7 +8810,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="124" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>44</v>
       </c>
@@ -8828,7 +8827,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>45</v>
       </c>
@@ -8845,7 +8844,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>196</v>
       </c>
@@ -8862,7 +8861,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>201</v>
       </c>
@@ -8896,7 +8895,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="129" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>202</v>
       </c>
@@ -8913,7 +8912,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="130" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>78</v>
       </c>
@@ -8930,7 +8929,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="131" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>63</v>
       </c>
@@ -8947,7 +8946,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="132" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>181</v>
       </c>
@@ -8964,7 +8963,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="133" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>184</v>
       </c>
@@ -8981,7 +8980,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="134" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>182</v>
       </c>
@@ -9015,7 +9014,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="136" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>99</v>
       </c>
@@ -9032,7 +9031,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="137" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>98</v>
       </c>
@@ -9049,7 +9048,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="138" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>17</v>
       </c>
@@ -9066,7 +9065,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="139" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>15</v>
       </c>
@@ -9083,7 +9082,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="140" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>16</v>
       </c>
@@ -9100,7 +9099,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="141" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>90</v>
       </c>
@@ -9117,7 +9116,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="142" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>88</v>
       </c>
@@ -9134,7 +9133,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="143" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>91</v>
       </c>
@@ -9151,7 +9150,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="144" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>89</v>
       </c>
@@ -9168,7 +9167,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="145" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>109</v>
       </c>
@@ -9185,7 +9184,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="146" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>107</v>
       </c>
@@ -9202,7 +9201,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="147" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>110</v>
       </c>
@@ -9219,7 +9218,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="148" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>108</v>
       </c>
@@ -9236,7 +9235,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="149" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>79</v>
       </c>
@@ -9253,7 +9252,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="150" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>65</v>
       </c>
@@ -9270,7 +9269,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="151" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>20</v>
       </c>
@@ -9287,7 +9286,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="152" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>21</v>
       </c>
@@ -9304,7 +9303,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="153" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>22</v>
       </c>
@@ -9321,7 +9320,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="154" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>23</v>
       </c>
@@ -9338,7 +9337,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="155" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>67</v>
       </c>
@@ -9355,7 +9354,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>68</v>
       </c>
@@ -9372,7 +9371,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="157" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>69</v>
       </c>
@@ -9389,7 +9388,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="158" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>70</v>
       </c>
@@ -9406,7 +9405,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="159" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>71</v>
       </c>
@@ -9423,7 +9422,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="160" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>72</v>
       </c>
@@ -9440,7 +9439,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="161" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>180</v>
       </c>
@@ -9457,7 +9456,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="162" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>178</v>
       </c>
@@ -9474,7 +9473,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="163" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>179</v>
       </c>
@@ -9491,7 +9490,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="164" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>177</v>
       </c>
@@ -9508,7 +9507,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="165" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>175</v>
       </c>
@@ -9525,7 +9524,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="166" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>170</v>
       </c>
@@ -9542,7 +9541,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="167" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>172</v>
       </c>
@@ -9559,7 +9558,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="168" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>174</v>
       </c>
@@ -9627,7 +9626,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="172" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>60</v>
       </c>
@@ -9644,7 +9643,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="173" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>59</v>
       </c>
@@ -9661,7 +9660,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="174" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>32</v>
       </c>
@@ -9678,7 +9677,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="175" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>33</v>
       </c>
@@ -9695,7 +9694,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="176" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>34</v>
       </c>
@@ -9712,7 +9711,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="177" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>30</v>
       </c>
@@ -9729,7 +9728,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="178" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>31</v>
       </c>
@@ -9746,7 +9745,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="179" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>35</v>
       </c>
@@ -9763,7 +9762,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="180" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>114</v>
       </c>
@@ -9780,7 +9779,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="181" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>113</v>
       </c>
@@ -9797,7 +9796,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="182" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>112</v>
       </c>
@@ -9814,7 +9813,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="183" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>111</v>
       </c>
@@ -9831,7 +9830,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="184" spans="1:5" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>36</v>
       </c>
@@ -9848,7 +9847,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="185" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>6</v>
       </c>
@@ -9865,7 +9864,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="186" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>9</v>
       </c>
@@ -9882,7 +9881,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="187" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>11</v>
       </c>
@@ -9899,7 +9898,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="188" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>7</v>
       </c>
@@ -9916,7 +9915,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="189" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>10</v>
       </c>
@@ -9933,7 +9932,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="190" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>5</v>
       </c>
@@ -9950,7 +9949,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="191" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>8</v>
       </c>
@@ -9984,7 +9983,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="193" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>73</v>
       </c>
@@ -10001,7 +10000,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="194" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>83</v>
       </c>
@@ -10018,7 +10017,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="195" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>84</v>
       </c>
@@ -10035,7 +10034,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="196" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A196" s="6" t="s">
         <v>2047</v>
       </c>
@@ -10049,7 +10048,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="197" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>193</v>
       </c>
@@ -10066,7 +10065,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="198" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>92</v>
       </c>
@@ -10083,7 +10082,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="199" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>93</v>
       </c>
@@ -10100,7 +10099,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="200" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>94</v>
       </c>
@@ -10117,7 +10116,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="201" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>95</v>
       </c>
@@ -10134,7 +10133,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="202" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>96</v>
       </c>
@@ -10151,7 +10150,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="203" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>97</v>
       </c>
@@ -10168,7 +10167,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="204" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>24</v>
       </c>
@@ -10185,7 +10184,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="205" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>25</v>
       </c>
@@ -10202,7 +10201,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="206" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>26</v>
       </c>
@@ -10219,7 +10218,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="207" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>27</v>
       </c>
@@ -10236,7 +10235,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="208" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>28</v>
       </c>
@@ -10253,7 +10252,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="209" spans="1:5" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>29</v>
       </c>
@@ -10270,7 +10269,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="210" spans="1:5" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>81</v>
       </c>
@@ -10287,7 +10286,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="211" spans="1:5" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>80</v>
       </c>
@@ -10304,7 +10303,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="212" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>82</v>
       </c>
@@ -10321,7 +10320,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="213" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>14</v>
       </c>
@@ -10339,28 +10338,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E213" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="cb:agrc:consumer_savings:cons_ag_land_value:X"/>
-        <filter val="cb:agrc:technical_savings:cons_ag:X"/>
-        <filter val="cb:agrc:technical_savings:producer_food_waste:X"/>
-        <filter val="cb:entc:technical_savings:electricity:opex"/>
-        <filter val="cb:inen:technical_savings:fuel_switch:all"/>
-        <filter val="cb:inen:technical_savings:fuel_switch:hi_heat"/>
-        <filter val="cb:inen:technical_savings:fuel_switch:lo_heat"/>
-        <filter val="cb:pflo:consumer_savings:better_diets:X"/>
-        <filter val="cb:scoe:technical_savings:fuel_switch:heat_pumps"/>
-        <filter val="cb:trns:technical_savings:electrification:hdv_vehicles"/>
-        <filter val="cb:trns:technical_savings:electrification:LDV"/>
-        <filter val="cb:trns:technical_savings:electrification:rail"/>
-        <filter val="cb:waso:consumer_savings:consumer_food_waste:X"/>
-      </filters>
-    </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E213">
-      <sortCondition ref="A1:A213"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:E213" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <hyperlinks>
     <hyperlink ref="C212" r:id="rId1" location=":~:text=Using%20the%20World%20Bank%20numbers,case%20of%20U.S.%20LMOP%20landfills." xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>

--- a/ssp_modeling/cost-benefits/cb_config_files/cb_config_params.xlsx
+++ b/ssp_modeling/cost-benefits/cb_config_files/cb_config_params.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_libya/ssp_modeling/cost-benefits/cb_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DFB0F81-4B49-3C40-BA96-CCBA4A139C98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{185424CE-4166-1349-A4B4-52EEA144DF4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-39500" yWindow="-7160" windowWidth="31780" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-43220" yWindow="-7160" windowWidth="35500" windowHeight="28200" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tx_table" sheetId="1" r:id="rId1"/>
@@ -24670,7 +24670,7 @@
         <v>791</v>
       </c>
       <c r="I37" s="9">
-        <v>-19</v>
+        <v>100</v>
       </c>
       <c r="J37" s="9" t="s">
         <v>590</v>
@@ -24717,7 +24717,7 @@
         <v>791</v>
       </c>
       <c r="I38">
-        <v>-500</v>
+        <v>1700</v>
       </c>
       <c r="J38" t="s">
         <v>590</v>

--- a/ssp_modeling/cost-benefits/cb_config_files/cb_config_params.xlsx
+++ b/ssp_modeling/cost-benefits/cb_config_files/cb_config_params.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_libya/ssp_modeling/cost-benefits/cb_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{901E5893-A590-4B4B-84D2-12AF8DBF0A88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B35EE093-F499-FA49-A3DE-AC6A4A955202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30480" yWindow="-620" windowWidth="30240" windowHeight="18980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="-620" windowWidth="38400" windowHeight="21000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tx_table" sheetId="1" r:id="rId1"/>
@@ -6300,7 +6300,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6355,12 +6355,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -6393,7 +6387,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -6411,7 +6405,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -16947,1914 +16940,1914 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>453</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
+      <c r="A2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C2" s="3">
+        <v>400</v>
       </c>
       <c r="D2" t="s">
-        <v>349</v>
+        <v>590</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>220</v>
+        <v>252</v>
       </c>
       <c r="G2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>349</v>
+        <v>629</v>
       </c>
       <c r="I2" t="s">
-        <v>349</v>
+        <v>678</v>
       </c>
       <c r="J2" t="s">
+        <v>352</v>
+      </c>
+      <c r="K2" t="s">
+        <v>687</v>
+      </c>
+      <c r="L2" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="C3" s="3">
         <v>350</v>
       </c>
-      <c r="K2" t="s">
-        <v>686</v>
-      </c>
-      <c r="L2" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>518</v>
-      </c>
-      <c r="C3" s="11">
-        <v>-150</v>
-      </c>
       <c r="D3" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>281</v>
+        <v>253</v>
       </c>
       <c r="G3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>653</v>
+        <v>630</v>
       </c>
       <c r="I3" t="s">
-        <v>394</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>356</v>
+        <v>678</v>
+      </c>
+      <c r="J3" t="s">
+        <v>352</v>
       </c>
       <c r="K3" t="s">
         <v>687</v>
       </c>
       <c r="L3" t="s">
-        <v>706</v>
+        <v>698</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>516</v>
-      </c>
-      <c r="C4" s="11">
-        <v>-50</v>
+      <c r="A4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="C4" s="3">
+        <v>500</v>
       </c>
       <c r="D4" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="G4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>652</v>
+        <v>631</v>
       </c>
       <c r="I4" t="s">
-        <v>394</v>
+        <v>678</v>
       </c>
       <c r="J4" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="K4" t="s">
         <v>687</v>
       </c>
       <c r="L4" t="s">
-        <v>706</v>
+        <v>698</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>517</v>
-      </c>
-      <c r="C5" s="11">
-        <v>-150</v>
+      <c r="A5" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="C5" s="3">
+        <v>500</v>
       </c>
       <c r="D5" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>280</v>
+        <v>255</v>
       </c>
       <c r="G5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>653</v>
+        <v>632</v>
       </c>
       <c r="I5" t="s">
-        <v>394</v>
+        <v>678</v>
       </c>
       <c r="J5" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K5" t="s">
         <v>687</v>
       </c>
       <c r="L5" t="s">
-        <v>706</v>
+        <v>698</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" t="s">
-        <v>468</v>
-      </c>
-      <c r="C6">
-        <v>-7</v>
+      <c r="A6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="C6" s="3">
+        <v>600</v>
       </c>
       <c r="D6" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="G6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>617</v>
+        <v>629</v>
       </c>
       <c r="I6" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="J6" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K6" t="s">
         <v>687</v>
       </c>
       <c r="L6" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" t="s">
-        <v>467</v>
-      </c>
-      <c r="C7">
-        <v>-7</v>
+      <c r="A7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="C7" s="3">
+        <v>900</v>
       </c>
       <c r="D7" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>234</v>
+        <v>257</v>
       </c>
       <c r="G7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>616</v>
+        <v>633</v>
       </c>
       <c r="I7" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="J7" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K7" t="s">
         <v>687</v>
       </c>
       <c r="L7" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" t="s">
-        <v>466</v>
-      </c>
-      <c r="C8">
-        <v>-30</v>
+      <c r="A8" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="C8" s="3">
+        <v>500</v>
       </c>
       <c r="D8" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="E8">
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>233</v>
+        <v>258</v>
       </c>
       <c r="G8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>615</v>
+        <v>629</v>
       </c>
       <c r="I8" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="J8" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K8" t="s">
         <v>687</v>
       </c>
       <c r="L8" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" t="s">
-        <v>465</v>
-      </c>
-      <c r="C9">
-        <v>-30</v>
+      <c r="A9" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="C9" s="3">
+        <v>550</v>
       </c>
       <c r="D9" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>232</v>
+        <v>259</v>
       </c>
       <c r="G9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>614</v>
+        <v>629</v>
       </c>
       <c r="I9" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="J9" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K9" t="s">
         <v>687</v>
       </c>
       <c r="L9" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" t="s">
-        <v>464</v>
-      </c>
-      <c r="C10">
-        <v>-30</v>
+      <c r="A10" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="C10" s="3">
+        <v>800</v>
       </c>
       <c r="D10" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="E10">
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>231</v>
+        <v>260</v>
       </c>
       <c r="G10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>613</v>
+        <v>634</v>
       </c>
       <c r="I10" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="J10" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K10" t="s">
         <v>687</v>
       </c>
       <c r="L10" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" t="s">
-        <v>463</v>
-      </c>
-      <c r="C11">
-        <v>-30</v>
+      <c r="A11" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0</v>
       </c>
       <c r="D11" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>230</v>
+        <v>261</v>
       </c>
       <c r="G11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>612</v>
+        <v>635</v>
       </c>
       <c r="I11" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="J11" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K11" t="s">
         <v>687</v>
       </c>
       <c r="L11" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>97</v>
-      </c>
-      <c r="B12" t="s">
-        <v>468</v>
-      </c>
-      <c r="C12">
-        <v>-30</v>
+      <c r="A12" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0</v>
       </c>
       <c r="D12" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="E12">
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>291</v>
+        <v>262</v>
       </c>
       <c r="G12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>661</v>
+        <v>636</v>
       </c>
       <c r="I12" t="s">
-        <v>397</v>
+        <v>678</v>
       </c>
       <c r="J12" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K12" t="s">
         <v>687</v>
       </c>
       <c r="L12" t="s">
-        <v>709</v>
+        <v>698</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>96</v>
-      </c>
-      <c r="B13" t="s">
-        <v>467</v>
-      </c>
-      <c r="C13">
-        <v>-30</v>
+      <c r="A13" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="C13" s="3">
+        <v>400</v>
       </c>
       <c r="D13" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>290</v>
+        <v>263</v>
       </c>
       <c r="G13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>661</v>
+        <v>637</v>
       </c>
       <c r="I13" t="s">
-        <v>397</v>
+        <v>678</v>
       </c>
       <c r="J13" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K13" t="s">
         <v>687</v>
       </c>
       <c r="L13" t="s">
-        <v>709</v>
+        <v>698</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>95</v>
-      </c>
-      <c r="B14" t="s">
-        <v>466</v>
-      </c>
-      <c r="C14">
-        <v>-30</v>
+      <c r="A14" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="C14" s="3">
+        <v>600</v>
       </c>
       <c r="D14" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>289</v>
+        <v>264</v>
       </c>
       <c r="G14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>661</v>
+        <v>638</v>
       </c>
       <c r="I14" t="s">
-        <v>397</v>
+        <v>678</v>
       </c>
       <c r="J14" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K14" t="s">
         <v>687</v>
       </c>
       <c r="L14" t="s">
-        <v>709</v>
+        <v>698</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="B15" t="s">
-        <v>465</v>
+        <v>512</v>
       </c>
       <c r="C15">
-        <v>-30</v>
+        <v>-1000000</v>
       </c>
       <c r="D15" t="s">
-        <v>587</v>
+        <v>349</v>
       </c>
       <c r="E15">
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>288</v>
+        <v>266</v>
       </c>
       <c r="G15" t="b">
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>661</v>
+        <v>349</v>
       </c>
       <c r="I15" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="J15" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K15" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L15" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="B16" t="s">
-        <v>464</v>
+        <v>499</v>
       </c>
       <c r="C16">
-        <v>-30</v>
+        <v>-500000</v>
       </c>
       <c r="D16" t="s">
-        <v>587</v>
+        <v>349</v>
       </c>
       <c r="E16">
         <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>287</v>
+        <v>266</v>
       </c>
       <c r="G16" t="b">
         <v>1</v>
       </c>
       <c r="H16" t="s">
-        <v>661</v>
+        <v>641</v>
       </c>
       <c r="I16" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="J16" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K16" t="s">
         <v>687</v>
       </c>
       <c r="L16" t="s">
-        <v>709</v>
+        <v>700</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="B17" t="s">
-        <v>463</v>
+        <v>536</v>
       </c>
       <c r="C17">
-        <v>-30</v>
+        <v>-500000</v>
       </c>
       <c r="D17" t="s">
-        <v>587</v>
+        <v>349</v>
       </c>
       <c r="E17">
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="G17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>661</v>
+        <v>641</v>
       </c>
       <c r="I17" t="s">
-        <v>397</v>
+        <v>379</v>
       </c>
       <c r="J17" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="K17" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L17" t="s">
-        <v>709</v>
+        <v>716</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>84</v>
+        <v>117</v>
       </c>
       <c r="B18" t="s">
-        <v>518</v>
+        <v>537</v>
       </c>
       <c r="C18">
-        <v>323.52941179999999</v>
+        <v>-500000</v>
       </c>
       <c r="D18" t="s">
-        <v>595</v>
+        <v>349</v>
       </c>
       <c r="E18">
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="G18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>653</v>
+        <v>641</v>
       </c>
       <c r="I18" t="s">
-        <v>394</v>
+        <v>379</v>
       </c>
       <c r="J18" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="K18" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L18" t="s">
-        <v>706</v>
+        <v>716</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="B19" t="s">
-        <v>517</v>
+        <v>538</v>
       </c>
       <c r="C19">
-        <v>323.52941179999999</v>
+        <v>-500000</v>
       </c>
       <c r="D19" t="s">
-        <v>595</v>
+        <v>349</v>
       </c>
       <c r="E19">
         <v>1</v>
       </c>
       <c r="F19" t="s">
-        <v>280</v>
+        <v>299</v>
       </c>
       <c r="G19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>653</v>
+        <v>641</v>
       </c>
       <c r="I19" t="s">
-        <v>394</v>
+        <v>379</v>
       </c>
       <c r="J19" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="K19" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L19" t="s">
-        <v>706</v>
+        <v>716</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="B20" t="s">
-        <v>467</v>
+        <v>539</v>
       </c>
       <c r="C20">
-        <v>-100</v>
+        <v>-500000</v>
       </c>
       <c r="D20" t="s">
-        <v>590</v>
+        <v>349</v>
       </c>
       <c r="E20">
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="G20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>649</v>
+        <v>641</v>
       </c>
       <c r="I20" t="s">
-        <v>392</v>
+        <v>379</v>
       </c>
       <c r="J20" t="s">
+        <v>361</v>
+      </c>
+      <c r="K20" t="s">
+        <v>686</v>
+      </c>
+      <c r="L20" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>120</v>
+      </c>
+      <c r="B21" t="s">
+        <v>540</v>
+      </c>
+      <c r="C21">
+        <v>-500000</v>
+      </c>
+      <c r="D21" t="s">
         <v>349</v>
       </c>
-      <c r="K20" t="s">
-        <v>687</v>
-      </c>
-      <c r="L20" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A21" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>446</v>
-      </c>
-      <c r="C21" s="13">
-        <v>-6.5</v>
-      </c>
-      <c r="D21" t="s">
-        <v>583</v>
-      </c>
       <c r="E21">
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>213</v>
+        <v>299</v>
       </c>
       <c r="G21" t="b">
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>597</v>
+        <v>641</v>
       </c>
       <c r="I21" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="J21" t="s">
-        <v>349</v>
+        <v>362</v>
       </c>
       <c r="K21" t="s">
         <v>686</v>
       </c>
       <c r="L21" t="s">
-        <v>689</v>
+        <v>716</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A22" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>443</v>
-      </c>
-      <c r="C22" s="13">
-        <v>-6.5</v>
+      <c r="A22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B22" t="s">
+        <v>541</v>
+      </c>
+      <c r="C22">
+        <v>-500000</v>
       </c>
       <c r="D22" t="s">
-        <v>583</v>
+        <v>349</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>210</v>
+        <v>299</v>
       </c>
       <c r="G22" t="b">
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>597</v>
+        <v>641</v>
       </c>
       <c r="I22" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="J22" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="K22" t="s">
         <v>686</v>
       </c>
       <c r="L22" t="s">
-        <v>689</v>
+        <v>716</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A23" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>448</v>
-      </c>
-      <c r="C23" s="13">
-        <v>-6.5</v>
+      <c r="A23" t="s">
+        <v>122</v>
+      </c>
+      <c r="B23" t="s">
+        <v>542</v>
+      </c>
+      <c r="C23">
+        <v>-500000</v>
       </c>
       <c r="D23" t="s">
-        <v>583</v>
+        <v>349</v>
       </c>
       <c r="E23">
         <v>1</v>
       </c>
       <c r="F23" t="s">
-        <v>215</v>
+        <v>299</v>
       </c>
       <c r="G23" t="b">
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>601</v>
+        <v>641</v>
       </c>
       <c r="I23" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="J23" t="s">
-        <v>349</v>
+        <v>364</v>
       </c>
       <c r="K23" t="s">
         <v>686</v>
       </c>
       <c r="L23" t="s">
-        <v>689</v>
+        <v>716</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A24" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>445</v>
-      </c>
-      <c r="C24" s="13">
-        <v>-6.5</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>583</v>
-      </c>
-      <c r="E24" s="3">
-        <v>1</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="G24" s="3" t="b">
+      <c r="A24" t="s">
+        <v>123</v>
+      </c>
+      <c r="B24" t="s">
+        <v>543</v>
+      </c>
+      <c r="C24">
+        <v>-500000</v>
+      </c>
+      <c r="D24" t="s">
+        <v>349</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24" t="s">
+        <v>299</v>
+      </c>
+      <c r="G24" t="b">
         <v>0</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>599</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="J24" s="3" t="s">
+      <c r="H24" t="s">
+        <v>641</v>
+      </c>
+      <c r="I24" t="s">
+        <v>379</v>
+      </c>
+      <c r="J24" t="s">
+        <v>365</v>
+      </c>
+      <c r="K24" t="s">
+        <v>686</v>
+      </c>
+      <c r="L24" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>124</v>
+      </c>
+      <c r="B25" t="s">
+        <v>544</v>
+      </c>
+      <c r="C25">
+        <v>-500000</v>
+      </c>
+      <c r="D25" t="s">
         <v>349</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>686</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A25" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>449</v>
-      </c>
-      <c r="C25" s="13">
-        <v>0</v>
-      </c>
-      <c r="D25" t="s">
-        <v>583</v>
-      </c>
       <c r="E25">
         <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>216</v>
+        <v>299</v>
       </c>
       <c r="G25" t="b">
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>349</v>
+        <v>641</v>
       </c>
       <c r="I25" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="J25" t="s">
-        <v>349</v>
+        <v>366</v>
       </c>
       <c r="K25" t="s">
         <v>686</v>
       </c>
       <c r="L25" t="s">
-        <v>689</v>
+        <v>716</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A26" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>447</v>
-      </c>
-      <c r="C26" s="13">
-        <v>-10</v>
+      <c r="A26" t="s">
+        <v>125</v>
+      </c>
+      <c r="B26" t="s">
+        <v>545</v>
+      </c>
+      <c r="C26">
+        <v>-500000</v>
       </c>
       <c r="D26" t="s">
-        <v>583</v>
+        <v>349</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>214</v>
+        <v>299</v>
       </c>
       <c r="G26" t="b">
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>600</v>
+        <v>641</v>
       </c>
       <c r="I26" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="J26" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="K26" t="s">
         <v>686</v>
       </c>
       <c r="L26" t="s">
-        <v>689</v>
+        <v>716</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A27" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="B27" s="13" t="s">
-        <v>444</v>
-      </c>
-      <c r="C27" s="13">
-        <v>-10</v>
+      <c r="A27" t="s">
+        <v>126</v>
+      </c>
+      <c r="B27" t="s">
+        <v>546</v>
+      </c>
+      <c r="C27">
+        <v>-500000</v>
       </c>
       <c r="D27" t="s">
-        <v>583</v>
+        <v>349</v>
       </c>
       <c r="E27">
         <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>211</v>
+        <v>299</v>
       </c>
       <c r="G27" t="b">
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>598</v>
+        <v>641</v>
       </c>
       <c r="I27" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="J27" t="s">
-        <v>349</v>
+        <v>367</v>
       </c>
       <c r="K27" t="s">
         <v>686</v>
       </c>
       <c r="L27" t="s">
-        <v>689</v>
+        <v>716</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A28" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="B28" s="13" t="s">
-        <v>475</v>
-      </c>
-      <c r="C28" s="13">
-        <v>200</v>
+      <c r="A28" t="s">
+        <v>127</v>
+      </c>
+      <c r="B28" t="s">
+        <v>547</v>
+      </c>
+      <c r="C28">
+        <v>-500000</v>
       </c>
       <c r="D28" t="s">
-        <v>583</v>
+        <v>349</v>
       </c>
       <c r="E28">
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>242</v>
+        <v>299</v>
       </c>
       <c r="G28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>623</v>
+        <v>641</v>
       </c>
       <c r="I28" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="J28" t="s">
-        <v>349</v>
+        <v>368</v>
       </c>
       <c r="K28" t="s">
         <v>686</v>
       </c>
       <c r="L28" t="s">
-        <v>697</v>
+        <v>716</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="B29" t="s">
-        <v>531</v>
+        <v>548</v>
       </c>
       <c r="C29">
-        <v>45000</v>
+        <v>-500000</v>
       </c>
       <c r="D29" t="s">
-        <v>590</v>
+        <v>349</v>
       </c>
       <c r="E29">
         <v>1</v>
       </c>
       <c r="F29" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="G29" t="b">
         <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>671</v>
+        <v>641</v>
       </c>
       <c r="I29" t="s">
-        <v>685</v>
+        <v>379</v>
       </c>
       <c r="J29" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="K29" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L29" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="B30" t="s">
-        <v>532</v>
+        <v>549</v>
       </c>
       <c r="C30">
-        <v>18000</v>
+        <v>-500000</v>
       </c>
       <c r="D30" t="s">
-        <v>590</v>
+        <v>349</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="G30" t="b">
         <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>672</v>
+        <v>641</v>
       </c>
       <c r="I30" t="s">
-        <v>685</v>
+        <v>379</v>
       </c>
       <c r="J30" t="s">
-        <v>350</v>
+        <v>369</v>
       </c>
       <c r="K30" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L30" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B31" t="s">
-        <v>533</v>
+        <v>550</v>
       </c>
       <c r="C31">
-        <v>130</v>
+        <v>-500000</v>
       </c>
       <c r="D31" t="s">
-        <v>590</v>
+        <v>349</v>
       </c>
       <c r="E31">
         <v>1</v>
       </c>
       <c r="F31" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="G31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" t="s">
-        <v>673</v>
+        <v>641</v>
       </c>
       <c r="I31" t="s">
-        <v>685</v>
+        <v>379</v>
       </c>
       <c r="J31" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="K31" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L31" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="B32" t="s">
-        <v>534</v>
+        <v>551</v>
       </c>
       <c r="C32">
-        <v>60</v>
+        <v>-500000</v>
       </c>
       <c r="D32" t="s">
-        <v>590</v>
+        <v>349</v>
       </c>
       <c r="E32">
         <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="G32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" t="s">
-        <v>674</v>
+        <v>641</v>
       </c>
       <c r="I32" t="s">
-        <v>685</v>
+        <v>379</v>
       </c>
       <c r="J32" t="s">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="K32" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L32" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>35</v>
+        <v>132</v>
       </c>
       <c r="B33" t="s">
-        <v>474</v>
+        <v>552</v>
       </c>
       <c r="C33">
-        <v>-0.06</v>
+        <v>-500000</v>
       </c>
       <c r="D33" t="s">
-        <v>588</v>
+        <v>349</v>
       </c>
       <c r="E33">
         <v>1</v>
       </c>
       <c r="F33" t="s">
-        <v>241</v>
+        <v>299</v>
       </c>
       <c r="G33" t="b">
         <v>0</v>
       </c>
       <c r="H33" t="s">
-        <v>622</v>
+        <v>641</v>
       </c>
       <c r="I33" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="J33" t="s">
-        <v>351</v>
+        <v>371</v>
       </c>
       <c r="K33" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L33" t="s">
-        <v>696</v>
+        <v>716</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>31</v>
+        <v>133</v>
       </c>
       <c r="B34" t="s">
-        <v>470</v>
+        <v>553</v>
       </c>
       <c r="C34">
-        <v>-1.2</v>
+        <v>-500000</v>
       </c>
       <c r="D34" t="s">
-        <v>588</v>
+        <v>349</v>
       </c>
       <c r="E34">
         <v>1</v>
       </c>
       <c r="F34" t="s">
-        <v>237</v>
+        <v>299</v>
       </c>
       <c r="G34" t="b">
         <v>0</v>
       </c>
       <c r="H34" t="s">
-        <v>619</v>
+        <v>641</v>
       </c>
       <c r="I34" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="J34" t="s">
-        <v>351</v>
+        <v>372</v>
       </c>
       <c r="K34" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L34" t="s">
-        <v>696</v>
+        <v>716</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>30</v>
+        <v>134</v>
       </c>
       <c r="B35" t="s">
-        <v>469</v>
+        <v>554</v>
       </c>
       <c r="C35">
-        <v>-1.2</v>
+        <v>-500000</v>
       </c>
       <c r="D35" t="s">
-        <v>588</v>
+        <v>349</v>
       </c>
       <c r="E35">
         <v>1</v>
       </c>
       <c r="F35" t="s">
-        <v>236</v>
+        <v>299</v>
       </c>
       <c r="G35" t="b">
         <v>0</v>
       </c>
       <c r="H35" t="s">
-        <v>618</v>
+        <v>641</v>
       </c>
       <c r="I35" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="J35" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="K35" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L35" t="s">
-        <v>696</v>
+        <v>716</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>34</v>
+        <v>135</v>
       </c>
       <c r="B36" t="s">
-        <v>473</v>
+        <v>555</v>
       </c>
       <c r="C36">
-        <v>-1.1000000000000001</v>
+        <v>-500000</v>
       </c>
       <c r="D36" t="s">
-        <v>588</v>
+        <v>349</v>
       </c>
       <c r="E36">
         <v>1</v>
       </c>
       <c r="F36" t="s">
-        <v>240</v>
+        <v>299</v>
       </c>
       <c r="G36" t="b">
         <v>0</v>
       </c>
       <c r="H36" t="s">
-        <v>621</v>
+        <v>641</v>
       </c>
       <c r="I36" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="J36" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="K36" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L36" t="s">
-        <v>696</v>
+        <v>716</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>33</v>
+        <v>136</v>
       </c>
       <c r="B37" t="s">
-        <v>472</v>
+        <v>556</v>
       </c>
       <c r="C37">
-        <v>-1.1000000000000001</v>
+        <v>-500000</v>
       </c>
       <c r="D37" t="s">
-        <v>588</v>
+        <v>349</v>
       </c>
       <c r="E37">
         <v>1</v>
       </c>
       <c r="F37" t="s">
-        <v>239</v>
+        <v>299</v>
       </c>
       <c r="G37" t="b">
         <v>0</v>
       </c>
       <c r="H37" t="s">
-        <v>621</v>
+        <v>641</v>
       </c>
       <c r="I37" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="J37" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="K37" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L37" t="s">
-        <v>696</v>
+        <v>716</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>32</v>
+        <v>137</v>
       </c>
       <c r="B38" t="s">
-        <v>471</v>
+        <v>557</v>
       </c>
       <c r="C38">
-        <v>-0.45</v>
+        <v>-500000</v>
       </c>
       <c r="D38" t="s">
-        <v>588</v>
+        <v>349</v>
       </c>
       <c r="E38">
         <v>1</v>
       </c>
       <c r="F38" t="s">
-        <v>238</v>
+        <v>299</v>
       </c>
       <c r="G38" t="b">
         <v>0</v>
       </c>
       <c r="H38" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="I38" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="J38" t="s">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="K38" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L38" t="s">
-        <v>696</v>
+        <v>716</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>59</v>
+        <v>138</v>
       </c>
       <c r="B39" t="s">
-        <v>498</v>
+        <v>558</v>
       </c>
       <c r="C39">
-        <v>-250</v>
+        <v>-500000</v>
       </c>
       <c r="D39" t="s">
-        <v>591</v>
+        <v>349</v>
       </c>
       <c r="E39">
         <v>1</v>
       </c>
       <c r="F39" t="s">
-        <v>265</v>
+        <v>299</v>
       </c>
       <c r="G39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="I39" t="s">
-        <v>349</v>
+        <v>379</v>
       </c>
       <c r="J39" t="s">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="K39" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L39" t="s">
-        <v>699</v>
+        <v>716</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>60</v>
+        <v>139</v>
       </c>
       <c r="B40" t="s">
-        <v>498</v>
+        <v>559</v>
       </c>
       <c r="C40">
-        <v>323.52941179999999</v>
+        <v>-500000</v>
       </c>
       <c r="D40" t="s">
-        <v>591</v>
+        <v>349</v>
       </c>
       <c r="E40">
         <v>1</v>
       </c>
       <c r="F40" t="s">
-        <v>265</v>
+        <v>299</v>
       </c>
       <c r="G40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="I40" t="s">
-        <v>349</v>
+        <v>379</v>
       </c>
       <c r="J40" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="K40" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L40" t="s">
-        <v>699</v>
+        <v>716</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>72</v>
+        <v>140</v>
       </c>
       <c r="B41" t="s">
-        <v>510</v>
+        <v>560</v>
       </c>
       <c r="C41">
-        <v>-0.08</v>
+        <v>-500000</v>
       </c>
       <c r="D41" t="s">
-        <v>594</v>
+        <v>349</v>
       </c>
       <c r="E41">
         <v>1</v>
       </c>
       <c r="F41" t="s">
-        <v>277</v>
+        <v>299</v>
       </c>
       <c r="G41" t="b">
         <v>0</v>
       </c>
       <c r="H41" t="s">
-        <v>648</v>
+        <v>641</v>
       </c>
       <c r="I41" t="s">
-        <v>680</v>
+        <v>379</v>
       </c>
       <c r="J41" t="s">
-        <v>350</v>
+        <v>367</v>
       </c>
       <c r="K41" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L41" t="s">
-        <v>702</v>
+        <v>716</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>71</v>
+        <v>141</v>
       </c>
       <c r="B42" t="s">
-        <v>509</v>
+        <v>561</v>
       </c>
       <c r="C42">
-        <v>-3</v>
+        <v>-500000</v>
       </c>
       <c r="D42" t="s">
-        <v>594</v>
+        <v>349</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>276</v>
+        <v>299</v>
       </c>
       <c r="G42" t="b">
         <v>0</v>
       </c>
       <c r="H42" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="I42" t="s">
-        <v>680</v>
+        <v>379</v>
       </c>
       <c r="J42" t="s">
-        <v>350</v>
+        <v>368</v>
       </c>
       <c r="K42" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L42" t="s">
-        <v>702</v>
+        <v>716</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>70</v>
+        <v>142</v>
       </c>
       <c r="B43" t="s">
-        <v>508</v>
+        <v>562</v>
       </c>
       <c r="C43">
-        <v>-8</v>
+        <v>-500000</v>
       </c>
       <c r="D43" t="s">
-        <v>594</v>
+        <v>349</v>
       </c>
       <c r="E43">
         <v>1</v>
       </c>
       <c r="F43" t="s">
-        <v>275</v>
+        <v>299</v>
       </c>
       <c r="G43" t="b">
         <v>0</v>
       </c>
       <c r="H43" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="I43" t="s">
-        <v>680</v>
+        <v>379</v>
       </c>
       <c r="J43" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="K43" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L43" t="s">
-        <v>702</v>
+        <v>716</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>69</v>
+        <v>143</v>
       </c>
       <c r="B44" t="s">
-        <v>507</v>
+        <v>563</v>
       </c>
       <c r="C44">
-        <v>-3.5</v>
+        <v>-500000</v>
       </c>
       <c r="D44" t="s">
-        <v>594</v>
+        <v>349</v>
       </c>
       <c r="E44">
         <v>1</v>
       </c>
       <c r="F44" t="s">
-        <v>274</v>
+        <v>299</v>
       </c>
       <c r="G44" t="b">
         <v>0</v>
       </c>
       <c r="H44" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="I44" t="s">
-        <v>680</v>
+        <v>379</v>
       </c>
       <c r="J44" t="s">
-        <v>350</v>
+        <v>369</v>
       </c>
       <c r="K44" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L44" t="s">
-        <v>702</v>
+        <v>716</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>68</v>
+        <v>144</v>
       </c>
       <c r="B45" t="s">
-        <v>506</v>
+        <v>564</v>
       </c>
       <c r="C45">
-        <v>-0.01</v>
+        <v>-500000</v>
       </c>
       <c r="D45" t="s">
-        <v>594</v>
+        <v>349</v>
       </c>
       <c r="E45">
         <v>1</v>
       </c>
       <c r="F45" t="s">
-        <v>273</v>
+        <v>299</v>
       </c>
       <c r="G45" t="b">
         <v>0</v>
       </c>
       <c r="H45" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="I45" t="s">
-        <v>680</v>
+        <v>379</v>
       </c>
       <c r="J45" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="K45" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L45" t="s">
-        <v>702</v>
+        <v>716</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>67</v>
+        <v>145</v>
       </c>
       <c r="B46" t="s">
-        <v>505</v>
+        <v>565</v>
       </c>
       <c r="C46">
-        <v>-0.04</v>
+        <v>-500000</v>
       </c>
       <c r="D46" t="s">
-        <v>593</v>
+        <v>349</v>
       </c>
       <c r="E46">
         <v>1</v>
       </c>
       <c r="F46" t="s">
-        <v>272</v>
+        <v>299</v>
       </c>
       <c r="G46" t="b">
         <v>0</v>
       </c>
       <c r="H46" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="I46" t="s">
-        <v>680</v>
+        <v>379</v>
       </c>
       <c r="J46" t="s">
-        <v>350</v>
+        <v>371</v>
       </c>
       <c r="K46" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L46" t="s">
-        <v>702</v>
+        <v>716</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>23</v>
+        <v>146</v>
       </c>
       <c r="B47" t="s">
-        <v>462</v>
+        <v>566</v>
       </c>
       <c r="C47">
-        <v>-12000</v>
+        <v>-500000</v>
       </c>
       <c r="D47" t="s">
-        <v>586</v>
+        <v>349</v>
       </c>
       <c r="E47">
         <v>1</v>
       </c>
       <c r="F47" t="s">
-        <v>229</v>
+        <v>299</v>
       </c>
       <c r="G47" t="b">
         <v>0</v>
       </c>
       <c r="H47" t="s">
-        <v>611</v>
+        <v>641</v>
       </c>
       <c r="I47" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="J47" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="K47" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L47" t="s">
-        <v>694</v>
+        <v>716</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>22</v>
+        <v>147</v>
       </c>
       <c r="B48" t="s">
-        <v>461</v>
+        <v>567</v>
       </c>
       <c r="C48">
-        <v>-75000</v>
+        <v>-500000</v>
       </c>
       <c r="D48" t="s">
-        <v>586</v>
+        <v>349</v>
       </c>
       <c r="E48">
         <v>1</v>
       </c>
       <c r="F48" t="s">
-        <v>228</v>
+        <v>299</v>
       </c>
       <c r="G48" t="b">
         <v>0</v>
       </c>
       <c r="H48" t="s">
-        <v>610</v>
+        <v>641</v>
       </c>
       <c r="I48" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="J48" t="s">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="K48" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L48" t="s">
-        <v>694</v>
+        <v>716</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>21</v>
+        <v>148</v>
       </c>
       <c r="B49" t="s">
-        <v>460</v>
+        <v>568</v>
       </c>
       <c r="C49">
-        <v>-18000</v>
+        <v>-500000</v>
       </c>
       <c r="D49" t="s">
-        <v>586</v>
+        <v>349</v>
       </c>
       <c r="E49">
         <v>1</v>
       </c>
       <c r="F49" t="s">
-        <v>227</v>
+        <v>299</v>
       </c>
       <c r="G49" t="b">
         <v>0</v>
       </c>
       <c r="H49" t="s">
-        <v>609</v>
+        <v>641</v>
       </c>
       <c r="I49" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="J49" t="s">
-        <v>350</v>
+        <v>366</v>
       </c>
       <c r="K49" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L49" t="s">
-        <v>694</v>
+        <v>716</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>20</v>
+        <v>149</v>
       </c>
       <c r="B50" t="s">
-        <v>459</v>
+        <v>569</v>
       </c>
       <c r="C50">
         <v>-500000</v>
       </c>
       <c r="D50" t="s">
-        <v>586</v>
+        <v>349</v>
       </c>
       <c r="E50">
         <v>1</v>
       </c>
       <c r="F50" t="s">
-        <v>226</v>
+        <v>299</v>
       </c>
       <c r="G50" t="b">
         <v>0</v>
       </c>
       <c r="H50" t="s">
-        <v>608</v>
+        <v>641</v>
       </c>
       <c r="I50" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="J50" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="K50" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L50" t="s">
-        <v>694</v>
+        <v>716</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A51" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="C51" s="3">
+      <c r="A51" t="s">
+        <v>150</v>
+      </c>
+      <c r="B51" t="s">
+        <v>570</v>
+      </c>
+      <c r="C51">
         <v>-500000</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="D51" t="s">
         <v>349</v>
       </c>
-      <c r="E51" s="3">
-        <v>1</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="G51" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="H51" s="3" t="s">
+      <c r="E51">
+        <v>1</v>
+      </c>
+      <c r="F51" t="s">
+        <v>299</v>
+      </c>
+      <c r="G51" t="b">
+        <v>0</v>
+      </c>
+      <c r="H51" t="s">
         <v>641</v>
       </c>
-      <c r="I51" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="K51" s="3" t="s">
-        <v>687</v>
-      </c>
-      <c r="L51" s="3" t="s">
-        <v>700</v>
+      <c r="I51" t="s">
+        <v>379</v>
+      </c>
+      <c r="J51" t="s">
+        <v>367</v>
+      </c>
+      <c r="K51" t="s">
+        <v>686</v>
+      </c>
+      <c r="L51" t="s">
+        <v>716</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>79</v>
+        <v>151</v>
       </c>
       <c r="B52" t="s">
-        <v>515</v>
+        <v>571</v>
       </c>
       <c r="C52">
-        <v>-1000000</v>
+        <v>-500000</v>
       </c>
       <c r="D52" t="s">
         <v>349</v>
@@ -18863,1042 +18856,1042 @@
         <v>1</v>
       </c>
       <c r="F52" t="s">
-        <v>270</v>
+        <v>299</v>
       </c>
       <c r="G52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H52" t="s">
-        <v>349</v>
+        <v>641</v>
       </c>
       <c r="I52" t="s">
-        <v>393</v>
+        <v>379</v>
       </c>
       <c r="J52" t="s">
-        <v>350</v>
+        <v>368</v>
       </c>
       <c r="K52" t="s">
         <v>686</v>
       </c>
       <c r="L52" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>108</v>
+        <v>152</v>
       </c>
       <c r="B53" t="s">
-        <v>455</v>
+        <v>572</v>
       </c>
       <c r="C53">
-        <v>-12000000</v>
+        <v>-500000</v>
       </c>
       <c r="D53" t="s">
-        <v>584</v>
+        <v>349</v>
       </c>
       <c r="E53">
         <v>1</v>
       </c>
       <c r="F53" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G53" t="b">
         <v>0</v>
       </c>
       <c r="H53" t="s">
-        <v>668</v>
+        <v>641</v>
       </c>
       <c r="I53" t="s">
-        <v>684</v>
+        <v>379</v>
       </c>
       <c r="J53" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="K53" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L53" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>110</v>
+        <v>153</v>
       </c>
       <c r="B54" t="s">
-        <v>522</v>
+        <v>573</v>
       </c>
       <c r="C54">
-        <v>-3000000</v>
+        <v>-500000</v>
       </c>
       <c r="D54" t="s">
-        <v>584</v>
+        <v>349</v>
       </c>
       <c r="E54">
         <v>1</v>
       </c>
       <c r="F54" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G54" t="b">
         <v>0</v>
       </c>
       <c r="H54" t="s">
-        <v>670</v>
+        <v>641</v>
       </c>
       <c r="I54" t="s">
-        <v>684</v>
+        <v>379</v>
       </c>
       <c r="J54" t="s">
-        <v>350</v>
+        <v>369</v>
       </c>
       <c r="K54" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L54" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="B55" t="s">
-        <v>454</v>
+        <v>574</v>
       </c>
       <c r="C55">
-        <v>-6000000</v>
+        <v>-500000</v>
       </c>
       <c r="D55" t="s">
-        <v>584</v>
+        <v>349</v>
       </c>
       <c r="E55">
         <v>1</v>
       </c>
       <c r="F55" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G55" t="b">
         <v>0</v>
       </c>
       <c r="H55" t="s">
-        <v>657</v>
+        <v>641</v>
       </c>
       <c r="I55" t="s">
-        <v>684</v>
+        <v>379</v>
       </c>
       <c r="J55" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="K55" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L55" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>109</v>
+        <v>155</v>
       </c>
       <c r="B56" t="s">
-        <v>456</v>
+        <v>575</v>
       </c>
       <c r="C56">
-        <v>-12000000</v>
+        <v>-500000</v>
       </c>
       <c r="D56" t="s">
-        <v>584</v>
+        <v>349</v>
       </c>
       <c r="E56">
         <v>1</v>
       </c>
       <c r="F56" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G56" t="b">
         <v>0</v>
       </c>
       <c r="H56" t="s">
-        <v>669</v>
+        <v>641</v>
       </c>
       <c r="I56" t="s">
-        <v>684</v>
+        <v>379</v>
       </c>
       <c r="J56" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="K56" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L56" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>89</v>
+        <v>156</v>
       </c>
       <c r="B57" t="s">
-        <v>455</v>
+        <v>576</v>
       </c>
       <c r="C57">
-        <v>-3000000</v>
+        <v>-500000</v>
       </c>
       <c r="D57" t="s">
-        <v>584</v>
+        <v>349</v>
       </c>
       <c r="E57">
         <v>1</v>
       </c>
       <c r="F57" t="s">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="G57" t="b">
         <v>0</v>
       </c>
       <c r="H57" t="s">
-        <v>658</v>
+        <v>641</v>
       </c>
       <c r="I57" t="s">
-        <v>682</v>
+        <v>379</v>
       </c>
       <c r="J57" t="s">
-        <v>350</v>
+        <v>366</v>
       </c>
       <c r="K57" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L57" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>91</v>
+        <v>157</v>
       </c>
       <c r="B58" t="s">
-        <v>522</v>
+        <v>577</v>
       </c>
       <c r="C58">
-        <v>-750000</v>
+        <v>-500000</v>
       </c>
       <c r="D58" t="s">
-        <v>584</v>
+        <v>349</v>
       </c>
       <c r="E58">
         <v>1</v>
       </c>
       <c r="F58" t="s">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="G58" t="b">
         <v>0</v>
       </c>
       <c r="H58" t="s">
-        <v>660</v>
+        <v>641</v>
       </c>
       <c r="I58" t="s">
-        <v>682</v>
+        <v>379</v>
       </c>
       <c r="J58" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="K58" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L58" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>88</v>
+        <v>158</v>
       </c>
       <c r="B59" t="s">
-        <v>454</v>
+        <v>578</v>
       </c>
       <c r="C59">
-        <v>-2500000</v>
+        <v>-500000</v>
       </c>
       <c r="D59" t="s">
-        <v>584</v>
+        <v>349</v>
       </c>
       <c r="E59">
         <v>1</v>
       </c>
       <c r="F59" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="G59" t="b">
         <v>0</v>
       </c>
       <c r="H59" t="s">
-        <v>657</v>
+        <v>641</v>
       </c>
       <c r="I59" t="s">
-        <v>682</v>
+        <v>379</v>
       </c>
       <c r="J59" t="s">
-        <v>350</v>
+        <v>367</v>
       </c>
       <c r="K59" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L59" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>90</v>
+        <v>159</v>
       </c>
       <c r="B60" t="s">
-        <v>456</v>
+        <v>579</v>
       </c>
       <c r="C60">
-        <v>-3000000</v>
+        <v>-500000</v>
       </c>
       <c r="D60" t="s">
-        <v>584</v>
+        <v>349</v>
       </c>
       <c r="E60">
         <v>1</v>
       </c>
       <c r="F60" t="s">
-        <v>284</v>
+        <v>299</v>
       </c>
       <c r="G60" t="b">
         <v>0</v>
       </c>
       <c r="H60" t="s">
-        <v>659</v>
+        <v>641</v>
       </c>
       <c r="I60" t="s">
-        <v>682</v>
+        <v>379</v>
       </c>
       <c r="J60" t="s">
-        <v>350</v>
+        <v>368</v>
       </c>
       <c r="K60" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L60" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>16</v>
+        <v>160</v>
       </c>
       <c r="B61" t="s">
-        <v>455</v>
+        <v>580</v>
       </c>
       <c r="C61">
-        <v>-750000</v>
+        <v>-500000</v>
       </c>
       <c r="D61" t="s">
-        <v>584</v>
+        <v>349</v>
       </c>
       <c r="E61">
         <v>1</v>
       </c>
       <c r="F61" t="s">
-        <v>222</v>
+        <v>299</v>
       </c>
       <c r="G61" t="b">
         <v>0</v>
       </c>
       <c r="H61" t="s">
-        <v>604</v>
+        <v>641</v>
       </c>
       <c r="I61" t="s">
-        <v>676</v>
+        <v>379</v>
       </c>
       <c r="J61" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="K61" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L61" t="s">
-        <v>692</v>
+        <v>716</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>15</v>
+        <v>161</v>
       </c>
       <c r="B62" t="s">
-        <v>454</v>
+        <v>581</v>
       </c>
       <c r="C62">
-        <v>-5500000</v>
+        <v>-500000</v>
       </c>
       <c r="D62" t="s">
-        <v>584</v>
+        <v>349</v>
       </c>
       <c r="E62">
         <v>1</v>
       </c>
       <c r="F62" t="s">
-        <v>221</v>
+        <v>299</v>
       </c>
       <c r="G62" t="b">
         <v>0</v>
       </c>
       <c r="H62" t="s">
-        <v>603</v>
+        <v>641</v>
       </c>
       <c r="I62" t="s">
-        <v>676</v>
+        <v>379</v>
       </c>
       <c r="J62" t="s">
-        <v>350</v>
+        <v>369</v>
       </c>
       <c r="K62" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L62" t="s">
-        <v>692</v>
+        <v>716</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>17</v>
+        <v>162</v>
       </c>
       <c r="B63" t="s">
-        <v>456</v>
+        <v>582</v>
       </c>
       <c r="C63">
-        <v>-750000</v>
+        <v>-500000</v>
       </c>
       <c r="D63" t="s">
-        <v>584</v>
+        <v>349</v>
       </c>
       <c r="E63">
         <v>1</v>
       </c>
       <c r="F63" t="s">
-        <v>223</v>
+        <v>299</v>
       </c>
       <c r="G63" t="b">
         <v>0</v>
       </c>
       <c r="H63" t="s">
-        <v>605</v>
+        <v>641</v>
       </c>
       <c r="I63" t="s">
-        <v>676</v>
+        <v>379</v>
       </c>
       <c r="J63" t="s">
+        <v>360</v>
+      </c>
+      <c r="K63" t="s">
+        <v>686</v>
+      </c>
+      <c r="L63" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A64" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="C64" s="3">
+        <v>-500</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="E64" s="3">
+        <v>1</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="G64" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="J64" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="K63" t="s">
-        <v>687</v>
-      </c>
-      <c r="L63" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
-        <v>98</v>
-      </c>
-      <c r="B64" t="s">
-        <v>523</v>
-      </c>
-      <c r="C64">
-        <v>-500000</v>
-      </c>
-      <c r="D64" t="s">
-        <v>596</v>
-      </c>
-      <c r="E64">
-        <v>1</v>
-      </c>
-      <c r="F64" t="s">
-        <v>292</v>
-      </c>
-      <c r="G64" t="b">
-        <v>0</v>
-      </c>
-      <c r="H64" t="s">
-        <v>662</v>
-      </c>
-      <c r="I64" t="s">
-        <v>398</v>
-      </c>
-      <c r="J64" t="s">
-        <v>350</v>
-      </c>
-      <c r="K64" t="s">
-        <v>687</v>
-      </c>
-      <c r="L64" t="s">
-        <v>710</v>
+      <c r="K64" s="3" t="s">
+        <v>688</v>
+      </c>
+      <c r="L64" s="3" t="s">
+        <v>712</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="B65" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C65">
-        <v>-70000</v>
+        <v>-1433486</v>
       </c>
       <c r="D65" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
       <c r="E65">
         <v>1</v>
       </c>
       <c r="F65" t="s">
-        <v>292</v>
+        <v>223</v>
       </c>
       <c r="G65" t="b">
         <v>0</v>
       </c>
       <c r="H65" t="s">
-        <v>663</v>
+        <v>656</v>
       </c>
       <c r="I65" t="s">
-        <v>399</v>
+        <v>681</v>
       </c>
       <c r="J65" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K65" t="s">
         <v>687</v>
       </c>
       <c r="L65" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A66" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>501</v>
-      </c>
-      <c r="C66" s="3">
-        <v>-500000</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="E66" s="3">
-        <v>1</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="G66" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>641</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="J66" s="3" t="s">
+      <c r="A66" t="s">
+        <v>85</v>
+      </c>
+      <c r="B66" t="s">
+        <v>519</v>
+      </c>
+      <c r="C66">
+        <v>-2768315</v>
+      </c>
+      <c r="D66" t="s">
+        <v>584</v>
+      </c>
+      <c r="E66">
+        <v>1</v>
+      </c>
+      <c r="F66" t="s">
+        <v>221</v>
+      </c>
+      <c r="G66" t="b">
+        <v>0</v>
+      </c>
+      <c r="H66" t="s">
+        <v>654</v>
+      </c>
+      <c r="I66" t="s">
+        <v>681</v>
+      </c>
+      <c r="J66" t="s">
         <v>350</v>
       </c>
-      <c r="K66" s="3" t="s">
+      <c r="K66" t="s">
         <v>687</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>700</v>
+      <c r="L66" t="s">
+        <v>707</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B67" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="C67">
-        <v>-1000000</v>
+        <v>-98656.5</v>
       </c>
       <c r="D67" t="s">
-        <v>349</v>
+        <v>584</v>
       </c>
       <c r="E67">
         <v>1</v>
       </c>
       <c r="F67" t="s">
-        <v>268</v>
+        <v>222</v>
       </c>
       <c r="G67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H67" t="s">
-        <v>349</v>
+        <v>655</v>
       </c>
       <c r="I67" t="s">
-        <v>393</v>
+        <v>681</v>
       </c>
       <c r="J67" t="s">
         <v>350</v>
       </c>
       <c r="K67" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L67" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
-        <v>45</v>
-      </c>
-      <c r="B68" t="s">
-        <v>484</v>
-      </c>
-      <c r="C68">
-        <v>80</v>
-      </c>
-      <c r="D68" t="s">
-        <v>589</v>
-      </c>
-      <c r="E68">
-        <v>1</v>
-      </c>
-      <c r="F68" t="s">
-        <v>251</v>
-      </c>
-      <c r="G68" t="b">
-        <v>0</v>
-      </c>
-      <c r="H68" t="s">
-        <v>626</v>
-      </c>
-      <c r="I68" t="s">
-        <v>678</v>
-      </c>
-      <c r="J68" t="s">
-        <v>352</v>
-      </c>
-      <c r="K68" t="s">
+      <c r="A68" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="C68" s="3">
+        <v>-500</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="E68" s="3">
+        <v>1</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="G68" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="K68" s="3" t="s">
         <v>687</v>
       </c>
-      <c r="L68" t="s">
-        <v>698</v>
+      <c r="L68" s="3" t="s">
+        <v>700</v>
       </c>
     </row>
     <row r="69" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>483</v>
+        <v>450</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>-1000000</v>
       </c>
       <c r="D69" t="s">
-        <v>589</v>
+        <v>349</v>
       </c>
       <c r="E69">
         <v>1</v>
       </c>
       <c r="F69" t="s">
-        <v>250</v>
+        <v>217</v>
       </c>
       <c r="G69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H69" t="s">
-        <v>628</v>
+        <v>349</v>
       </c>
       <c r="I69" t="s">
-        <v>678</v>
+        <v>379</v>
       </c>
       <c r="J69" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="K69" t="s">
         <v>687</v>
       </c>
       <c r="L69" t="s">
-        <v>698</v>
+        <v>690</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="B70" t="s">
-        <v>482</v>
+        <v>452</v>
       </c>
       <c r="C70">
-        <v>200</v>
+        <v>740000</v>
       </c>
       <c r="D70" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="E70">
         <v>1</v>
       </c>
       <c r="F70" t="s">
-        <v>249</v>
+        <v>219</v>
       </c>
       <c r="G70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H70" t="s">
-        <v>627</v>
+        <v>602</v>
       </c>
       <c r="I70" t="s">
-        <v>678</v>
+        <v>380</v>
       </c>
       <c r="J70" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="K70" t="s">
         <v>687</v>
       </c>
       <c r="L70" t="s">
-        <v>698</v>
+        <v>690</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>42</v>
+        <v>102</v>
       </c>
       <c r="B71" t="s">
-        <v>481</v>
+        <v>526</v>
       </c>
       <c r="C71">
-        <v>250</v>
+        <v>-3055862</v>
       </c>
       <c r="D71" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="E71">
         <v>1</v>
       </c>
       <c r="F71" t="s">
-        <v>248</v>
+        <v>295</v>
       </c>
       <c r="G71" t="b">
         <v>0</v>
       </c>
       <c r="H71" t="s">
-        <v>627</v>
+        <v>664</v>
       </c>
       <c r="I71" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="J71" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="K71" t="s">
         <v>687</v>
       </c>
       <c r="L71" t="s">
-        <v>698</v>
+        <v>711</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>41</v>
+        <v>103</v>
       </c>
       <c r="B72" t="s">
-        <v>480</v>
+        <v>527</v>
       </c>
       <c r="C72">
-        <v>60</v>
+        <v>-2468365</v>
       </c>
       <c r="D72" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="E72">
         <v>1</v>
       </c>
       <c r="F72" t="s">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="G72" t="b">
         <v>0</v>
       </c>
       <c r="H72" t="s">
-        <v>626</v>
+        <v>665</v>
       </c>
       <c r="I72" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="J72" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="K72" t="s">
         <v>687</v>
       </c>
       <c r="L72" t="s">
-        <v>698</v>
+        <v>711</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>40</v>
+        <v>104</v>
       </c>
       <c r="B73" t="s">
-        <v>479</v>
+        <v>528</v>
       </c>
       <c r="C73">
-        <v>4</v>
+        <v>-2468365</v>
       </c>
       <c r="D73" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="E73">
         <v>1</v>
       </c>
       <c r="F73" t="s">
-        <v>246</v>
+        <v>297</v>
       </c>
       <c r="G73" t="b">
         <v>0</v>
       </c>
       <c r="H73" t="s">
-        <v>625</v>
+        <v>666</v>
       </c>
       <c r="I73" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="J73" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="K73" t="s">
         <v>687</v>
       </c>
       <c r="L73" t="s">
-        <v>698</v>
+        <v>711</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>39</v>
+        <v>100</v>
       </c>
       <c r="B74" t="s">
-        <v>478</v>
+        <v>524</v>
       </c>
       <c r="C74">
-        <v>350</v>
+        <v>-8471713</v>
       </c>
       <c r="D74" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="E74">
         <v>1</v>
       </c>
       <c r="F74" t="s">
-        <v>245</v>
+        <v>293</v>
       </c>
       <c r="G74" t="b">
         <v>0</v>
       </c>
       <c r="H74" t="s">
-        <v>624</v>
+        <v>603</v>
       </c>
       <c r="I74" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="J74" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="K74" t="s">
         <v>687</v>
       </c>
       <c r="L74" t="s">
-        <v>698</v>
+        <v>711</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>38</v>
+        <v>101</v>
       </c>
       <c r="B75" t="s">
-        <v>477</v>
+        <v>525</v>
       </c>
       <c r="C75">
-        <v>400</v>
+        <v>-1161035</v>
       </c>
       <c r="D75" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="E75">
         <v>1</v>
       </c>
       <c r="F75" t="s">
-        <v>244</v>
+        <v>294</v>
       </c>
       <c r="G75" t="b">
         <v>0</v>
       </c>
       <c r="H75" t="s">
-        <v>624</v>
+        <v>604</v>
       </c>
       <c r="I75" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="J75" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="K75" t="s">
         <v>687</v>
       </c>
       <c r="L75" t="s">
-        <v>698</v>
+        <v>711</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>37</v>
+        <v>105</v>
       </c>
       <c r="B76" t="s">
-        <v>476</v>
+        <v>529</v>
       </c>
       <c r="C76">
-        <v>180</v>
+        <v>-122334</v>
       </c>
       <c r="D76" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="E76">
         <v>1</v>
       </c>
       <c r="F76" t="s">
-        <v>243</v>
+        <v>298</v>
       </c>
       <c r="G76" t="b">
         <v>0</v>
       </c>
       <c r="H76" t="s">
-        <v>624</v>
+        <v>667</v>
       </c>
       <c r="I76" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="J76" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="K76" t="s">
         <v>687</v>
       </c>
       <c r="L76" t="s">
-        <v>698</v>
+        <v>711</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="B77" t="s">
-        <v>535</v>
+        <v>513</v>
       </c>
       <c r="C77">
-        <v>300</v>
+        <v>-1000000</v>
       </c>
       <c r="D77" t="s">
-        <v>591</v>
+        <v>349</v>
       </c>
       <c r="E77">
         <v>1</v>
       </c>
       <c r="F77" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="G77" t="b">
         <v>1</v>
       </c>
       <c r="H77" t="s">
-        <v>675</v>
+        <v>349</v>
       </c>
       <c r="I77" t="s">
+        <v>393</v>
+      </c>
+      <c r="J77" t="s">
+        <v>350</v>
+      </c>
+      <c r="K77" t="s">
+        <v>686</v>
+      </c>
+      <c r="L77" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A78" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="C78" s="3">
+        <v>-500</v>
+      </c>
+      <c r="D78" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="J77" t="s">
-        <v>357</v>
-      </c>
-      <c r="K77" t="s">
+      <c r="E78" s="3">
+        <v>1</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="G78" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="J78" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="K78" s="3" t="s">
         <v>687</v>
       </c>
-      <c r="L77" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A78" t="s">
-        <v>19</v>
-      </c>
-      <c r="B78" t="s">
-        <v>458</v>
-      </c>
-      <c r="C78">
-        <v>100</v>
-      </c>
-      <c r="D78" t="s">
-        <v>585</v>
-      </c>
-      <c r="E78">
-        <v>1</v>
-      </c>
-      <c r="F78" t="s">
-        <v>225</v>
-      </c>
-      <c r="G78" t="b">
-        <v>0</v>
-      </c>
-      <c r="H78" t="s">
-        <v>607</v>
-      </c>
-      <c r="I78" t="s">
-        <v>383</v>
-      </c>
-      <c r="J78" t="s">
-        <v>350</v>
-      </c>
-      <c r="K78" t="s">
-        <v>687</v>
-      </c>
-      <c r="L78" t="s">
-        <v>693</v>
+      <c r="L78" s="3" t="s">
+        <v>700</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="B79" t="s">
-        <v>457</v>
+        <v>504</v>
       </c>
       <c r="C79">
-        <v>200</v>
+        <v>-45</v>
       </c>
       <c r="D79" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="E79">
         <v>1</v>
       </c>
       <c r="F79" t="s">
-        <v>224</v>
+        <v>271</v>
       </c>
       <c r="G79" t="b">
         <v>0</v>
       </c>
       <c r="H79" t="s">
-        <v>606</v>
+        <v>642</v>
       </c>
       <c r="I79" t="s">
-        <v>382</v>
+        <v>679</v>
       </c>
       <c r="J79" t="s">
         <v>350</v>
@@ -19907,18 +19900,18 @@
         <v>687</v>
       </c>
       <c r="L79" t="s">
-        <v>693</v>
+        <v>701</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B80" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="C80">
-        <v>-400</v>
+        <v>-85</v>
       </c>
       <c r="D80" t="s">
         <v>592</v>
@@ -19933,7 +19926,7 @@
         <v>0</v>
       </c>
       <c r="H80" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="I80" t="s">
         <v>679</v>
@@ -19950,13 +19943,13 @@
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B81" t="s">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="C81">
-        <v>-100</v>
+        <v>-370</v>
       </c>
       <c r="D81" t="s">
         <v>592</v>
@@ -19971,7 +19964,7 @@
         <v>0</v>
       </c>
       <c r="H81" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="I81" t="s">
         <v>679</v>
@@ -19988,31 +19981,31 @@
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="B82" t="s">
-        <v>504</v>
+        <v>457</v>
       </c>
       <c r="C82">
-        <v>-50</v>
+        <v>500</v>
       </c>
       <c r="D82" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="E82">
         <v>1</v>
       </c>
       <c r="F82" t="s">
-        <v>271</v>
+        <v>224</v>
       </c>
       <c r="G82" t="b">
         <v>0</v>
       </c>
       <c r="H82" t="s">
-        <v>642</v>
+        <v>606</v>
       </c>
       <c r="I82" t="s">
-        <v>679</v>
+        <v>382</v>
       </c>
       <c r="J82" t="s">
         <v>350</v>
@@ -20021,1006 +20014,1006 @@
         <v>687</v>
       </c>
       <c r="L82" t="s">
-        <v>701</v>
+        <v>693</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A83" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>500</v>
-      </c>
-      <c r="C83" s="3">
-        <v>-500000</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="E83" s="3">
-        <v>1</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="G83" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>641</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="J83" s="3" t="s">
+      <c r="A83" t="s">
+        <v>19</v>
+      </c>
+      <c r="B83" t="s">
+        <v>458</v>
+      </c>
+      <c r="C83">
+        <v>300</v>
+      </c>
+      <c r="D83" t="s">
+        <v>585</v>
+      </c>
+      <c r="E83">
+        <v>1</v>
+      </c>
+      <c r="F83" t="s">
+        <v>225</v>
+      </c>
+      <c r="G83" t="b">
+        <v>0</v>
+      </c>
+      <c r="H83" t="s">
+        <v>607</v>
+      </c>
+      <c r="I83" t="s">
+        <v>383</v>
+      </c>
+      <c r="J83" t="s">
         <v>350</v>
       </c>
-      <c r="K83" s="3" t="s">
+      <c r="K83" t="s">
         <v>687</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>700</v>
+      <c r="L83" t="s">
+        <v>693</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="B84" t="s">
-        <v>513</v>
+        <v>535</v>
       </c>
       <c r="C84">
-        <v>-1000000</v>
+        <v>323.52941179999999</v>
       </c>
       <c r="D84" t="s">
+        <v>591</v>
+      </c>
+      <c r="E84">
+        <v>1</v>
+      </c>
+      <c r="F84" t="s">
+        <v>265</v>
+      </c>
+      <c r="G84" t="b">
+        <v>1</v>
+      </c>
+      <c r="H84" t="s">
+        <v>675</v>
+      </c>
+      <c r="I84" t="s">
         <v>349</v>
       </c>
-      <c r="E84">
-        <v>1</v>
-      </c>
-      <c r="F84" t="s">
-        <v>267</v>
-      </c>
-      <c r="G84" t="b">
-        <v>1</v>
-      </c>
-      <c r="H84" t="s">
-        <v>349</v>
-      </c>
-      <c r="I84" t="s">
-        <v>393</v>
-      </c>
       <c r="J84" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="K84" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L84" t="s">
-        <v>705</v>
+        <v>715</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>105</v>
+        <v>37</v>
       </c>
       <c r="B85" t="s">
-        <v>529</v>
+        <v>476</v>
       </c>
       <c r="C85">
-        <v>-80000</v>
+        <v>260</v>
       </c>
       <c r="D85" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="E85">
         <v>1</v>
       </c>
       <c r="F85" t="s">
-        <v>298</v>
+        <v>243</v>
       </c>
       <c r="G85" t="b">
         <v>0</v>
       </c>
       <c r="H85" t="s">
-        <v>667</v>
+        <v>624</v>
       </c>
       <c r="I85" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="J85" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="K85" t="s">
         <v>687</v>
       </c>
       <c r="L85" t="s">
-        <v>711</v>
+        <v>698</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>101</v>
+        <v>38</v>
       </c>
       <c r="B86" t="s">
-        <v>525</v>
+        <v>477</v>
       </c>
       <c r="C86">
-        <v>-750000</v>
+        <v>260</v>
       </c>
       <c r="D86" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="E86">
         <v>1</v>
       </c>
       <c r="F86" t="s">
-        <v>294</v>
+        <v>244</v>
       </c>
       <c r="G86" t="b">
         <v>0</v>
       </c>
       <c r="H86" t="s">
-        <v>604</v>
+        <v>624</v>
       </c>
       <c r="I86" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="J86" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="K86" t="s">
         <v>687</v>
       </c>
       <c r="L86" t="s">
-        <v>711</v>
+        <v>698</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>100</v>
+        <v>39</v>
       </c>
       <c r="B87" t="s">
-        <v>524</v>
+        <v>478</v>
       </c>
       <c r="C87">
-        <v>-5500000</v>
+        <v>260</v>
       </c>
       <c r="D87" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="E87">
         <v>1</v>
       </c>
       <c r="F87" t="s">
-        <v>293</v>
+        <v>245</v>
       </c>
       <c r="G87" t="b">
         <v>0</v>
       </c>
       <c r="H87" t="s">
-        <v>603</v>
+        <v>624</v>
       </c>
       <c r="I87" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="J87" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="K87" t="s">
         <v>687</v>
       </c>
       <c r="L87" t="s">
-        <v>711</v>
+        <v>698</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>104</v>
+        <v>40</v>
       </c>
       <c r="B88" t="s">
-        <v>528</v>
+        <v>479</v>
       </c>
       <c r="C88">
-        <v>-1800000</v>
+        <v>2.6</v>
       </c>
       <c r="D88" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="E88">
         <v>1</v>
       </c>
       <c r="F88" t="s">
-        <v>297</v>
+        <v>246</v>
       </c>
       <c r="G88" t="b">
         <v>0</v>
       </c>
       <c r="H88" t="s">
-        <v>666</v>
+        <v>625</v>
       </c>
       <c r="I88" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="J88" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="K88" t="s">
         <v>687</v>
       </c>
       <c r="L88" t="s">
-        <v>711</v>
+        <v>698</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>103</v>
+        <v>41</v>
       </c>
       <c r="B89" t="s">
-        <v>527</v>
+        <v>480</v>
       </c>
       <c r="C89">
-        <v>-1800000</v>
+        <v>26</v>
       </c>
       <c r="D89" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="E89">
         <v>1</v>
       </c>
       <c r="F89" t="s">
-        <v>296</v>
+        <v>247</v>
       </c>
       <c r="G89" t="b">
         <v>0</v>
       </c>
       <c r="H89" t="s">
-        <v>665</v>
+        <v>626</v>
       </c>
       <c r="I89" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="J89" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="K89" t="s">
         <v>687</v>
       </c>
       <c r="L89" t="s">
-        <v>711</v>
+        <v>698</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>102</v>
+        <v>42</v>
       </c>
       <c r="B90" t="s">
-        <v>526</v>
+        <v>481</v>
       </c>
       <c r="C90">
-        <v>-2000000</v>
+        <v>200</v>
       </c>
       <c r="D90" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="E90">
         <v>1</v>
       </c>
       <c r="F90" t="s">
-        <v>295</v>
+        <v>248</v>
       </c>
       <c r="G90" t="b">
         <v>0</v>
       </c>
       <c r="H90" t="s">
-        <v>664</v>
+        <v>627</v>
       </c>
       <c r="I90" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="J90" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="K90" t="s">
         <v>687</v>
       </c>
       <c r="L90" t="s">
-        <v>711</v>
+        <v>698</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="B91" t="s">
-        <v>452</v>
+        <v>482</v>
       </c>
       <c r="C91">
-        <v>740000</v>
+        <v>200</v>
       </c>
       <c r="D91" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="E91">
         <v>1</v>
       </c>
       <c r="F91" t="s">
-        <v>219</v>
+        <v>249</v>
       </c>
       <c r="G91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H91" t="s">
-        <v>602</v>
+        <v>627</v>
       </c>
       <c r="I91" t="s">
-        <v>380</v>
+        <v>678</v>
       </c>
       <c r="J91" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K91" t="s">
         <v>687</v>
       </c>
       <c r="L91" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="B92" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="C92">
-        <v>-1000000</v>
+        <v>50</v>
       </c>
       <c r="D92" t="s">
-        <v>349</v>
+        <v>589</v>
       </c>
       <c r="E92">
         <v>1</v>
       </c>
       <c r="F92" t="s">
-        <v>217</v>
+        <v>250</v>
       </c>
       <c r="G92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H92" t="s">
-        <v>349</v>
+        <v>628</v>
       </c>
       <c r="I92" t="s">
-        <v>379</v>
+        <v>678</v>
       </c>
       <c r="J92" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="K92" t="s">
         <v>687</v>
       </c>
       <c r="L92" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A93" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="C93" s="3">
-        <v>-500000</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="E93" s="3">
-        <v>1</v>
-      </c>
-      <c r="F93" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="G93" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="H93" s="3" t="s">
-        <v>641</v>
-      </c>
-      <c r="I93" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="J93" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="K93" s="3" t="s">
+      <c r="A93" t="s">
+        <v>45</v>
+      </c>
+      <c r="B93" t="s">
+        <v>484</v>
+      </c>
+      <c r="C93">
+        <v>26</v>
+      </c>
+      <c r="D93" t="s">
+        <v>589</v>
+      </c>
+      <c r="E93">
+        <v>1</v>
+      </c>
+      <c r="F93" t="s">
+        <v>251</v>
+      </c>
+      <c r="G93" t="b">
+        <v>0</v>
+      </c>
+      <c r="H93" t="s">
+        <v>626</v>
+      </c>
+      <c r="I93" t="s">
+        <v>678</v>
+      </c>
+      <c r="J93" t="s">
+        <v>352</v>
+      </c>
+      <c r="K93" t="s">
         <v>687</v>
       </c>
-      <c r="L93" s="3" t="s">
-        <v>700</v>
+      <c r="L93" t="s">
+        <v>698</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="B94" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="C94">
-        <v>-65000</v>
+        <v>-1000000</v>
       </c>
       <c r="D94" t="s">
-        <v>584</v>
+        <v>349</v>
       </c>
       <c r="E94">
         <v>1</v>
       </c>
       <c r="F94" t="s">
-        <v>222</v>
+        <v>268</v>
       </c>
       <c r="G94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H94" t="s">
-        <v>655</v>
+        <v>349</v>
       </c>
       <c r="I94" t="s">
-        <v>681</v>
+        <v>393</v>
       </c>
       <c r="J94" t="s">
         <v>350</v>
       </c>
       <c r="K94" t="s">
+        <v>686</v>
+      </c>
+      <c r="L94" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A95" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="C95" s="3">
+        <v>-500</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="E95" s="3">
+        <v>1</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="G95" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="I95" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="J95" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="K95" s="3" t="s">
         <v>687</v>
       </c>
-      <c r="L94" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A95" t="s">
-        <v>85</v>
-      </c>
-      <c r="B95" t="s">
-        <v>519</v>
-      </c>
-      <c r="C95">
-        <v>-1800000</v>
-      </c>
-      <c r="D95" t="s">
-        <v>584</v>
-      </c>
-      <c r="E95">
-        <v>1</v>
-      </c>
-      <c r="F95" t="s">
-        <v>221</v>
-      </c>
-      <c r="G95" t="b">
-        <v>0</v>
-      </c>
-      <c r="H95" t="s">
-        <v>654</v>
-      </c>
-      <c r="I95" t="s">
-        <v>681</v>
-      </c>
-      <c r="J95" t="s">
-        <v>350</v>
-      </c>
-      <c r="K95" t="s">
-        <v>687</v>
-      </c>
-      <c r="L95" t="s">
-        <v>707</v>
+      <c r="L95" s="3" t="s">
+        <v>700</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="B96" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C96">
-        <v>-950000</v>
+        <v>-60000</v>
       </c>
       <c r="D96" t="s">
-        <v>584</v>
+        <v>596</v>
       </c>
       <c r="E96">
         <v>1</v>
       </c>
       <c r="F96" t="s">
-        <v>223</v>
+        <v>292</v>
       </c>
       <c r="G96" t="b">
         <v>0</v>
       </c>
       <c r="H96" t="s">
-        <v>656</v>
+        <v>663</v>
       </c>
       <c r="I96" t="s">
-        <v>681</v>
+        <v>399</v>
       </c>
       <c r="J96" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="K96" t="s">
         <v>687</v>
       </c>
       <c r="L96" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A97" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>530</v>
-      </c>
-      <c r="C97" s="3">
-        <v>-500000</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="E97" s="3">
-        <v>1</v>
-      </c>
-      <c r="F97" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="G97" s="3" t="b">
+      <c r="A97" t="s">
+        <v>98</v>
+      </c>
+      <c r="B97" t="s">
+        <v>523</v>
+      </c>
+      <c r="C97">
+        <v>-200000</v>
+      </c>
+      <c r="D97" t="s">
+        <v>596</v>
+      </c>
+      <c r="E97">
+        <v>1</v>
+      </c>
+      <c r="F97" t="s">
+        <v>292</v>
+      </c>
+      <c r="G97" t="b">
         <v>0</v>
       </c>
-      <c r="H97" s="3" t="s">
-        <v>641</v>
-      </c>
-      <c r="I97" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="J97" s="3" t="s">
+      <c r="H97" t="s">
+        <v>662</v>
+      </c>
+      <c r="I97" t="s">
+        <v>398</v>
+      </c>
+      <c r="J97" t="s">
         <v>350</v>
       </c>
-      <c r="K97" s="3" t="s">
-        <v>688</v>
-      </c>
-      <c r="L97" s="3" t="s">
-        <v>712</v>
+      <c r="K97" t="s">
+        <v>687</v>
+      </c>
+      <c r="L97" t="s">
+        <v>710</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>162</v>
+        <v>17</v>
       </c>
       <c r="B98" t="s">
-        <v>582</v>
+        <v>456</v>
       </c>
       <c r="C98">
-        <v>-500000</v>
+        <v>-1161035</v>
       </c>
       <c r="D98" t="s">
-        <v>349</v>
+        <v>584</v>
       </c>
       <c r="E98">
         <v>1</v>
       </c>
       <c r="F98" t="s">
-        <v>299</v>
+        <v>223</v>
       </c>
       <c r="G98" t="b">
         <v>0</v>
       </c>
       <c r="H98" t="s">
-        <v>641</v>
+        <v>605</v>
       </c>
       <c r="I98" t="s">
-        <v>379</v>
+        <v>676</v>
       </c>
       <c r="J98" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="K98" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L98" t="s">
-        <v>716</v>
+        <v>692</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>161</v>
+        <v>15</v>
       </c>
       <c r="B99" t="s">
-        <v>581</v>
+        <v>454</v>
       </c>
       <c r="C99">
-        <v>-500000</v>
+        <v>-8471713</v>
       </c>
       <c r="D99" t="s">
-        <v>349</v>
+        <v>584</v>
       </c>
       <c r="E99">
         <v>1</v>
       </c>
       <c r="F99" t="s">
-        <v>299</v>
+        <v>221</v>
       </c>
       <c r="G99" t="b">
         <v>0</v>
       </c>
       <c r="H99" t="s">
-        <v>641</v>
+        <v>603</v>
       </c>
       <c r="I99" t="s">
-        <v>379</v>
+        <v>676</v>
       </c>
       <c r="J99" t="s">
-        <v>369</v>
+        <v>350</v>
       </c>
       <c r="K99" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L99" t="s">
-        <v>716</v>
+        <v>692</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>160</v>
+        <v>16</v>
       </c>
       <c r="B100" t="s">
-        <v>580</v>
+        <v>455</v>
       </c>
       <c r="C100">
-        <v>-500000</v>
+        <v>-1161035</v>
       </c>
       <c r="D100" t="s">
-        <v>349</v>
+        <v>584</v>
       </c>
       <c r="E100">
         <v>1</v>
       </c>
       <c r="F100" t="s">
-        <v>299</v>
+        <v>222</v>
       </c>
       <c r="G100" t="b">
         <v>0</v>
       </c>
       <c r="H100" t="s">
-        <v>641</v>
+        <v>604</v>
       </c>
       <c r="I100" t="s">
-        <v>379</v>
+        <v>676</v>
       </c>
       <c r="J100" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="K100" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L100" t="s">
-        <v>716</v>
+        <v>692</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>159</v>
+        <v>90</v>
       </c>
       <c r="B101" t="s">
-        <v>579</v>
+        <v>456</v>
       </c>
       <c r="C101">
-        <v>-500000</v>
+        <v>-5712018</v>
       </c>
       <c r="D101" t="s">
-        <v>349</v>
+        <v>584</v>
       </c>
       <c r="E101">
         <v>1</v>
       </c>
       <c r="F101" t="s">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="G101" t="b">
         <v>0</v>
       </c>
       <c r="H101" t="s">
-        <v>641</v>
+        <v>659</v>
       </c>
       <c r="I101" t="s">
-        <v>379</v>
+        <v>682</v>
       </c>
       <c r="J101" t="s">
-        <v>368</v>
+        <v>350</v>
       </c>
       <c r="K101" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L101" t="s">
-        <v>716</v>
+        <v>708</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>158</v>
+        <v>88</v>
       </c>
       <c r="B102" t="s">
-        <v>578</v>
+        <v>454</v>
       </c>
       <c r="C102">
-        <v>-500000</v>
+        <v>-4656642</v>
       </c>
       <c r="D102" t="s">
-        <v>349</v>
+        <v>584</v>
       </c>
       <c r="E102">
         <v>1</v>
       </c>
       <c r="F102" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="G102" t="b">
         <v>0</v>
       </c>
       <c r="H102" t="s">
-        <v>641</v>
+        <v>657</v>
       </c>
       <c r="I102" t="s">
-        <v>379</v>
+        <v>682</v>
       </c>
       <c r="J102" t="s">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="K102" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L102" t="s">
-        <v>716</v>
+        <v>708</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>157</v>
+        <v>91</v>
       </c>
       <c r="B103" t="s">
-        <v>577</v>
+        <v>522</v>
       </c>
       <c r="C103">
-        <v>-500000</v>
+        <v>-1428005</v>
       </c>
       <c r="D103" t="s">
-        <v>349</v>
+        <v>584</v>
       </c>
       <c r="E103">
         <v>1</v>
       </c>
       <c r="F103" t="s">
-        <v>299</v>
+        <v>285</v>
       </c>
       <c r="G103" t="b">
         <v>0</v>
       </c>
       <c r="H103" t="s">
-        <v>641</v>
+        <v>660</v>
       </c>
       <c r="I103" t="s">
-        <v>379</v>
+        <v>682</v>
       </c>
       <c r="J103" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="K103" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L103" t="s">
-        <v>716</v>
+        <v>708</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>156</v>
+        <v>89</v>
       </c>
       <c r="B104" t="s">
-        <v>576</v>
+        <v>455</v>
       </c>
       <c r="C104">
-        <v>-500000</v>
+        <v>-5712018</v>
       </c>
       <c r="D104" t="s">
-        <v>349</v>
+        <v>584</v>
       </c>
       <c r="E104">
         <v>1</v>
       </c>
       <c r="F104" t="s">
-        <v>299</v>
+        <v>283</v>
       </c>
       <c r="G104" t="b">
         <v>0</v>
       </c>
       <c r="H104" t="s">
-        <v>641</v>
+        <v>658</v>
       </c>
       <c r="I104" t="s">
-        <v>379</v>
+        <v>682</v>
       </c>
       <c r="J104" t="s">
-        <v>366</v>
+        <v>350</v>
       </c>
       <c r="K104" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L104" t="s">
-        <v>716</v>
+        <v>708</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>155</v>
+        <v>109</v>
       </c>
       <c r="B105" t="s">
-        <v>575</v>
+        <v>456</v>
       </c>
       <c r="C105">
-        <v>-500000</v>
+        <v>-9817684</v>
       </c>
       <c r="D105" t="s">
-        <v>349</v>
+        <v>584</v>
       </c>
       <c r="E105">
         <v>1</v>
       </c>
       <c r="F105" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="G105" t="b">
         <v>0</v>
       </c>
       <c r="H105" t="s">
-        <v>641</v>
+        <v>669</v>
       </c>
       <c r="I105" t="s">
-        <v>379</v>
+        <v>684</v>
       </c>
       <c r="J105" t="s">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="K105" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L105" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>574</v>
+        <v>454</v>
       </c>
       <c r="C106">
-        <v>-500000</v>
+        <v>-4622358</v>
       </c>
       <c r="D106" t="s">
-        <v>349</v>
+        <v>584</v>
       </c>
       <c r="E106">
         <v>1</v>
       </c>
       <c r="F106" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G106" t="b">
         <v>0</v>
       </c>
       <c r="H106" t="s">
-        <v>641</v>
+        <v>657</v>
       </c>
       <c r="I106" t="s">
-        <v>379</v>
+        <v>684</v>
       </c>
       <c r="J106" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="K106" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L106" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>153</v>
+        <v>110</v>
       </c>
       <c r="B107" t="s">
-        <v>573</v>
+        <v>522</v>
       </c>
       <c r="C107">
-        <v>-500000</v>
+        <v>-2454421</v>
       </c>
       <c r="D107" t="s">
-        <v>349</v>
+        <v>584</v>
       </c>
       <c r="E107">
         <v>1</v>
       </c>
       <c r="F107" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="G107" t="b">
         <v>0</v>
       </c>
       <c r="H107" t="s">
-        <v>641</v>
+        <v>670</v>
       </c>
       <c r="I107" t="s">
-        <v>379</v>
+        <v>684</v>
       </c>
       <c r="J107" t="s">
-        <v>369</v>
+        <v>350</v>
       </c>
       <c r="K107" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L107" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>152</v>
+        <v>108</v>
       </c>
       <c r="B108" t="s">
-        <v>572</v>
+        <v>455</v>
       </c>
       <c r="C108">
-        <v>-500000</v>
+        <v>-9817684</v>
       </c>
       <c r="D108" t="s">
-        <v>349</v>
+        <v>584</v>
       </c>
       <c r="E108">
         <v>1</v>
       </c>
       <c r="F108" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="G108" t="b">
         <v>0</v>
       </c>
       <c r="H108" t="s">
-        <v>641</v>
+        <v>668</v>
       </c>
       <c r="I108" t="s">
-        <v>379</v>
+        <v>684</v>
       </c>
       <c r="J108" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="K108" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L108" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>151</v>
+        <v>79</v>
       </c>
       <c r="B109" t="s">
-        <v>571</v>
+        <v>515</v>
       </c>
       <c r="C109">
-        <v>-500000</v>
+        <v>-1000000</v>
       </c>
       <c r="D109" t="s">
         <v>349</v>
@@ -21029,1935 +21022,1938 @@
         <v>1</v>
       </c>
       <c r="F109" t="s">
-        <v>299</v>
+        <v>270</v>
       </c>
       <c r="G109" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H109" t="s">
-        <v>641</v>
+        <v>349</v>
       </c>
       <c r="I109" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="J109" t="s">
-        <v>368</v>
+        <v>350</v>
       </c>
       <c r="K109" t="s">
         <v>686</v>
       </c>
       <c r="L109" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A110" t="s">
-        <v>150</v>
-      </c>
-      <c r="B110" t="s">
-        <v>570</v>
-      </c>
-      <c r="C110">
-        <v>-500000</v>
-      </c>
-      <c r="D110" t="s">
+      <c r="A110" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="C110" s="3">
+        <v>-500</v>
+      </c>
+      <c r="D110" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="E110">
-        <v>1</v>
-      </c>
-      <c r="F110" t="s">
-        <v>299</v>
-      </c>
-      <c r="G110" t="b">
-        <v>0</v>
-      </c>
-      <c r="H110" t="s">
+      <c r="E110" s="3">
+        <v>1</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="G110" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="H110" s="3" t="s">
         <v>641</v>
       </c>
-      <c r="I110" t="s">
-        <v>379</v>
-      </c>
-      <c r="J110" t="s">
-        <v>367</v>
-      </c>
-      <c r="K110" t="s">
-        <v>686</v>
-      </c>
-      <c r="L110" t="s">
-        <v>716</v>
+      <c r="I110" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="J110" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="K110" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="L110" s="3" t="s">
+        <v>700</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>149</v>
+        <v>20</v>
       </c>
       <c r="B111" t="s">
-        <v>569</v>
+        <v>459</v>
       </c>
       <c r="C111">
-        <v>-500000</v>
+        <v>-410000</v>
       </c>
       <c r="D111" t="s">
-        <v>349</v>
+        <v>586</v>
       </c>
       <c r="E111">
         <v>1</v>
       </c>
       <c r="F111" t="s">
-        <v>299</v>
+        <v>226</v>
       </c>
       <c r="G111" t="b">
         <v>0</v>
       </c>
       <c r="H111" t="s">
-        <v>641</v>
+        <v>608</v>
       </c>
       <c r="I111" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="J111" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="K111" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L111" t="s">
-        <v>716</v>
+        <v>694</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>148</v>
+        <v>21</v>
       </c>
       <c r="B112" t="s">
-        <v>568</v>
+        <v>460</v>
       </c>
       <c r="C112">
-        <v>-500000</v>
+        <v>-14000</v>
       </c>
       <c r="D112" t="s">
-        <v>349</v>
+        <v>586</v>
       </c>
       <c r="E112">
         <v>1</v>
       </c>
       <c r="F112" t="s">
-        <v>299</v>
+        <v>227</v>
       </c>
       <c r="G112" t="b">
         <v>0</v>
       </c>
       <c r="H112" t="s">
-        <v>641</v>
+        <v>609</v>
       </c>
       <c r="I112" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="J112" t="s">
-        <v>366</v>
+        <v>350</v>
       </c>
       <c r="K112" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L112" t="s">
-        <v>716</v>
+        <v>694</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>147</v>
+        <v>22</v>
       </c>
       <c r="B113" t="s">
-        <v>567</v>
+        <v>461</v>
       </c>
       <c r="C113">
-        <v>-500000</v>
+        <v>-53000</v>
       </c>
       <c r="D113" t="s">
-        <v>349</v>
+        <v>586</v>
       </c>
       <c r="E113">
         <v>1</v>
       </c>
       <c r="F113" t="s">
-        <v>299</v>
+        <v>228</v>
       </c>
       <c r="G113" t="b">
         <v>0</v>
       </c>
       <c r="H113" t="s">
-        <v>641</v>
+        <v>610</v>
       </c>
       <c r="I113" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="J113" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="K113" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L113" t="s">
-        <v>716</v>
+        <v>694</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>146</v>
+        <v>23</v>
       </c>
       <c r="B114" t="s">
-        <v>566</v>
+        <v>462</v>
       </c>
       <c r="C114">
-        <v>-500000</v>
+        <v>-10000</v>
       </c>
       <c r="D114" t="s">
-        <v>349</v>
+        <v>586</v>
       </c>
       <c r="E114">
         <v>1</v>
       </c>
       <c r="F114" t="s">
-        <v>299</v>
+        <v>229</v>
       </c>
       <c r="G114" t="b">
         <v>0</v>
       </c>
       <c r="H114" t="s">
-        <v>641</v>
+        <v>611</v>
       </c>
       <c r="I114" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="J114" t="s">
-        <v>363</v>
+        <v>349</v>
       </c>
       <c r="K114" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L114" t="s">
-        <v>716</v>
+        <v>694</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>145</v>
+        <v>67</v>
       </c>
       <c r="B115" t="s">
-        <v>565</v>
+        <v>505</v>
       </c>
       <c r="C115">
-        <v>-500000</v>
+        <v>-0.06</v>
       </c>
       <c r="D115" t="s">
-        <v>349</v>
+        <v>593</v>
       </c>
       <c r="E115">
         <v>1</v>
       </c>
       <c r="F115" t="s">
-        <v>299</v>
+        <v>272</v>
       </c>
       <c r="G115" t="b">
         <v>0</v>
       </c>
       <c r="H115" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="I115" t="s">
-        <v>379</v>
+        <v>680</v>
       </c>
       <c r="J115" t="s">
-        <v>371</v>
+        <v>350</v>
       </c>
       <c r="K115" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L115" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>144</v>
+        <v>68</v>
       </c>
       <c r="B116" t="s">
-        <v>564</v>
+        <v>506</v>
       </c>
       <c r="C116">
-        <v>-500000</v>
+        <v>-1.7000000000000001E-2</v>
       </c>
       <c r="D116" t="s">
-        <v>349</v>
+        <v>594</v>
       </c>
       <c r="E116">
         <v>1</v>
       </c>
       <c r="F116" t="s">
-        <v>299</v>
+        <v>273</v>
       </c>
       <c r="G116" t="b">
         <v>0</v>
       </c>
       <c r="H116" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="I116" t="s">
-        <v>379</v>
+        <v>680</v>
       </c>
       <c r="J116" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="K116" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L116" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>143</v>
+        <v>69</v>
       </c>
       <c r="B117" t="s">
-        <v>563</v>
+        <v>507</v>
       </c>
       <c r="C117">
-        <v>-500000</v>
+        <v>-5.2</v>
       </c>
       <c r="D117" t="s">
-        <v>349</v>
+        <v>594</v>
       </c>
       <c r="E117">
         <v>1</v>
       </c>
       <c r="F117" t="s">
-        <v>299</v>
+        <v>274</v>
       </c>
       <c r="G117" t="b">
         <v>0</v>
       </c>
       <c r="H117" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="I117" t="s">
-        <v>379</v>
+        <v>680</v>
       </c>
       <c r="J117" t="s">
-        <v>369</v>
+        <v>350</v>
       </c>
       <c r="K117" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L117" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>142</v>
+        <v>70</v>
       </c>
       <c r="B118" t="s">
-        <v>562</v>
+        <v>508</v>
       </c>
       <c r="C118">
-        <v>-500000</v>
+        <v>-14</v>
       </c>
       <c r="D118" t="s">
-        <v>349</v>
+        <v>594</v>
       </c>
       <c r="E118">
         <v>1</v>
       </c>
       <c r="F118" t="s">
-        <v>299</v>
+        <v>275</v>
       </c>
       <c r="G118" t="b">
         <v>0</v>
       </c>
       <c r="H118" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="I118" t="s">
-        <v>379</v>
+        <v>680</v>
       </c>
       <c r="J118" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="K118" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L118" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>141</v>
+        <v>71</v>
       </c>
       <c r="B119" t="s">
-        <v>561</v>
+        <v>509</v>
       </c>
       <c r="C119">
-        <v>-500000</v>
+        <v>-5.2</v>
       </c>
       <c r="D119" t="s">
-        <v>349</v>
+        <v>594</v>
       </c>
       <c r="E119">
         <v>1</v>
       </c>
       <c r="F119" t="s">
-        <v>299</v>
+        <v>276</v>
       </c>
       <c r="G119" t="b">
         <v>0</v>
       </c>
       <c r="H119" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="I119" t="s">
-        <v>379</v>
+        <v>680</v>
       </c>
       <c r="J119" t="s">
-        <v>368</v>
+        <v>350</v>
       </c>
       <c r="K119" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L119" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>140</v>
+        <v>72</v>
       </c>
       <c r="B120" t="s">
-        <v>560</v>
+        <v>510</v>
       </c>
       <c r="C120">
-        <v>-500000</v>
+        <v>-0.17</v>
       </c>
       <c r="D120" t="s">
-        <v>349</v>
+        <v>594</v>
       </c>
       <c r="E120">
         <v>1</v>
       </c>
       <c r="F120" t="s">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="G120" t="b">
         <v>0</v>
       </c>
       <c r="H120" t="s">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="I120" t="s">
-        <v>379</v>
+        <v>680</v>
       </c>
       <c r="J120" t="s">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="K120" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L120" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>139</v>
+        <v>60</v>
       </c>
       <c r="B121" t="s">
-        <v>559</v>
+        <v>498</v>
       </c>
       <c r="C121">
-        <v>-500000</v>
+        <v>323.52941179999999</v>
       </c>
       <c r="D121" t="s">
+        <v>591</v>
+      </c>
+      <c r="E121">
+        <v>1</v>
+      </c>
+      <c r="F121" t="s">
+        <v>265</v>
+      </c>
+      <c r="G121" t="b">
+        <v>1</v>
+      </c>
+      <c r="H121" t="s">
+        <v>640</v>
+      </c>
+      <c r="I121" t="s">
         <v>349</v>
       </c>
-      <c r="E121">
-        <v>1</v>
-      </c>
-      <c r="F121" t="s">
-        <v>299</v>
-      </c>
-      <c r="G121" t="b">
-        <v>0</v>
-      </c>
-      <c r="H121" t="s">
-        <v>641</v>
-      </c>
-      <c r="I121" t="s">
-        <v>379</v>
-      </c>
       <c r="J121" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="K121" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L121" t="s">
-        <v>716</v>
+        <v>699</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="B122" t="s">
-        <v>558</v>
+        <v>498</v>
       </c>
       <c r="C122">
-        <v>-500000</v>
+        <v>-500</v>
       </c>
       <c r="D122" t="s">
+        <v>591</v>
+      </c>
+      <c r="E122">
+        <v>1</v>
+      </c>
+      <c r="F122" t="s">
+        <v>265</v>
+      </c>
+      <c r="G122" t="b">
+        <v>1</v>
+      </c>
+      <c r="H122" t="s">
+        <v>639</v>
+      </c>
+      <c r="I122" t="s">
         <v>349</v>
       </c>
-      <c r="E122">
-        <v>1</v>
-      </c>
-      <c r="F122" t="s">
-        <v>299</v>
-      </c>
-      <c r="G122" t="b">
-        <v>0</v>
-      </c>
-      <c r="H122" t="s">
-        <v>641</v>
-      </c>
-      <c r="I122" t="s">
-        <v>379</v>
-      </c>
       <c r="J122" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="K122" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L122" t="s">
-        <v>716</v>
+        <v>699</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>137</v>
+        <v>32</v>
       </c>
       <c r="B123" t="s">
-        <v>557</v>
+        <v>471</v>
       </c>
       <c r="C123">
-        <v>-500000</v>
+        <v>-0.64</v>
       </c>
       <c r="D123" t="s">
-        <v>349</v>
+        <v>588</v>
       </c>
       <c r="E123">
         <v>1</v>
       </c>
       <c r="F123" t="s">
-        <v>299</v>
+        <v>238</v>
       </c>
       <c r="G123" t="b">
         <v>0</v>
       </c>
       <c r="H123" t="s">
-        <v>641</v>
+        <v>620</v>
       </c>
       <c r="I123" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="J123" t="s">
-        <v>365</v>
+        <v>351</v>
       </c>
       <c r="K123" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L123" t="s">
-        <v>716</v>
+        <v>696</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>136</v>
+        <v>33</v>
       </c>
       <c r="B124" t="s">
-        <v>556</v>
+        <v>472</v>
       </c>
       <c r="C124">
-        <v>-500000</v>
+        <v>-1.44</v>
       </c>
       <c r="D124" t="s">
-        <v>349</v>
+        <v>588</v>
       </c>
       <c r="E124">
         <v>1</v>
       </c>
       <c r="F124" t="s">
-        <v>299</v>
+        <v>239</v>
       </c>
       <c r="G124" t="b">
         <v>0</v>
       </c>
       <c r="H124" t="s">
-        <v>641</v>
+        <v>621</v>
       </c>
       <c r="I124" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="J124" t="s">
-        <v>364</v>
+        <v>351</v>
       </c>
       <c r="K124" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L124" t="s">
-        <v>716</v>
+        <v>696</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>135</v>
+        <v>34</v>
       </c>
       <c r="B125" t="s">
-        <v>555</v>
+        <v>473</v>
       </c>
       <c r="C125">
-        <v>-500000</v>
+        <v>-1.44</v>
       </c>
       <c r="D125" t="s">
-        <v>349</v>
+        <v>588</v>
       </c>
       <c r="E125">
         <v>1</v>
       </c>
       <c r="F125" t="s">
-        <v>299</v>
+        <v>240</v>
       </c>
       <c r="G125" t="b">
         <v>0</v>
       </c>
       <c r="H125" t="s">
-        <v>641</v>
+        <v>621</v>
       </c>
       <c r="I125" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="J125" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="K125" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L125" t="s">
-        <v>716</v>
+        <v>696</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>134</v>
+        <v>30</v>
       </c>
       <c r="B126" t="s">
-        <v>554</v>
+        <v>469</v>
       </c>
       <c r="C126">
-        <v>-500000</v>
+        <v>-3.04</v>
       </c>
       <c r="D126" t="s">
-        <v>349</v>
+        <v>588</v>
       </c>
       <c r="E126">
         <v>1</v>
       </c>
       <c r="F126" t="s">
-        <v>299</v>
+        <v>236</v>
       </c>
       <c r="G126" t="b">
         <v>0</v>
       </c>
       <c r="H126" t="s">
-        <v>641</v>
+        <v>618</v>
       </c>
       <c r="I126" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="J126" t="s">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="K126" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L126" t="s">
-        <v>716</v>
+        <v>696</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>133</v>
+        <v>31</v>
       </c>
       <c r="B127" t="s">
-        <v>553</v>
+        <v>470</v>
       </c>
       <c r="C127">
-        <v>-500000</v>
+        <v>-3.04</v>
       </c>
       <c r="D127" t="s">
-        <v>349</v>
+        <v>588</v>
       </c>
       <c r="E127">
         <v>1</v>
       </c>
       <c r="F127" t="s">
-        <v>299</v>
+        <v>237</v>
       </c>
       <c r="G127" t="b">
         <v>0</v>
       </c>
       <c r="H127" t="s">
-        <v>641</v>
+        <v>619</v>
       </c>
       <c r="I127" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="J127" t="s">
-        <v>372</v>
+        <v>351</v>
       </c>
       <c r="K127" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L127" t="s">
-        <v>716</v>
+        <v>696</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>132</v>
+        <v>35</v>
       </c>
       <c r="B128" t="s">
-        <v>552</v>
+        <v>474</v>
       </c>
       <c r="C128">
-        <v>-500000</v>
+        <v>-0.06</v>
       </c>
       <c r="D128" t="s">
-        <v>349</v>
+        <v>588</v>
       </c>
       <c r="E128">
         <v>1</v>
       </c>
       <c r="F128" t="s">
-        <v>299</v>
+        <v>241</v>
       </c>
       <c r="G128" t="b">
         <v>0</v>
       </c>
       <c r="H128" t="s">
-        <v>641</v>
+        <v>622</v>
       </c>
       <c r="I128" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="J128" t="s">
-        <v>371</v>
+        <v>351</v>
       </c>
       <c r="K128" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L128" t="s">
-        <v>716</v>
+        <v>696</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="B129" t="s">
-        <v>551</v>
+        <v>534</v>
       </c>
       <c r="C129">
-        <v>-500000</v>
+        <v>60</v>
       </c>
       <c r="D129" t="s">
-        <v>349</v>
+        <v>590</v>
       </c>
       <c r="E129">
         <v>1</v>
       </c>
       <c r="F129" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="G129" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H129" t="s">
-        <v>641</v>
+        <v>674</v>
       </c>
       <c r="I129" t="s">
-        <v>379</v>
+        <v>685</v>
       </c>
       <c r="J129" t="s">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="K129" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L129" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
+        <v>113</v>
+      </c>
+      <c r="B130" t="s">
+        <v>533</v>
+      </c>
+      <c r="C130">
         <v>130</v>
       </c>
-      <c r="B130" t="s">
-        <v>550</v>
-      </c>
-      <c r="C130">
-        <v>-500000</v>
-      </c>
       <c r="D130" t="s">
-        <v>349</v>
+        <v>590</v>
       </c>
       <c r="E130">
         <v>1</v>
       </c>
       <c r="F130" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="G130" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H130" t="s">
-        <v>641</v>
+        <v>673</v>
       </c>
       <c r="I130" t="s">
-        <v>379</v>
+        <v>685</v>
       </c>
       <c r="J130" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="K130" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L130" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="B131" t="s">
-        <v>549</v>
+        <v>532</v>
       </c>
       <c r="C131">
-        <v>-500000</v>
+        <v>20000</v>
       </c>
       <c r="D131" t="s">
-        <v>349</v>
+        <v>590</v>
       </c>
       <c r="E131">
         <v>1</v>
       </c>
       <c r="F131" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="G131" t="b">
         <v>0</v>
       </c>
       <c r="H131" t="s">
-        <v>641</v>
+        <v>672</v>
       </c>
       <c r="I131" t="s">
-        <v>379</v>
+        <v>685</v>
       </c>
       <c r="J131" t="s">
-        <v>369</v>
+        <v>350</v>
       </c>
       <c r="K131" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L131" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="B132" t="s">
-        <v>548</v>
+        <v>531</v>
       </c>
       <c r="C132">
-        <v>-500000</v>
+        <v>51000</v>
       </c>
       <c r="D132" t="s">
-        <v>349</v>
+        <v>590</v>
       </c>
       <c r="E132">
         <v>1</v>
       </c>
       <c r="F132" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="G132" t="b">
         <v>0</v>
       </c>
       <c r="H132" t="s">
-        <v>641</v>
+        <v>671</v>
       </c>
       <c r="I132" t="s">
-        <v>379</v>
+        <v>685</v>
       </c>
       <c r="J132" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="K132" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L132" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>127</v>
+        <v>36</v>
       </c>
       <c r="B133" t="s">
-        <v>547</v>
+        <v>475</v>
       </c>
       <c r="C133">
-        <v>-500000</v>
+        <v>200</v>
       </c>
       <c r="D133" t="s">
+        <v>583</v>
+      </c>
+      <c r="E133">
+        <v>1</v>
+      </c>
+      <c r="F133" t="s">
+        <v>242</v>
+      </c>
+      <c r="G133" t="b">
+        <v>1</v>
+      </c>
+      <c r="H133" t="s">
+        <v>623</v>
+      </c>
+      <c r="I133" t="s">
+        <v>387</v>
+      </c>
+      <c r="J133" t="s">
         <v>349</v>
-      </c>
-      <c r="E133">
-        <v>1</v>
-      </c>
-      <c r="F133" t="s">
-        <v>299</v>
-      </c>
-      <c r="G133" t="b">
-        <v>0</v>
-      </c>
-      <c r="H133" t="s">
-        <v>641</v>
-      </c>
-      <c r="I133" t="s">
-        <v>379</v>
-      </c>
-      <c r="J133" t="s">
-        <v>368</v>
       </c>
       <c r="K133" t="s">
         <v>686</v>
       </c>
       <c r="L133" t="s">
-        <v>716</v>
+        <v>697</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>126</v>
+        <v>6</v>
       </c>
       <c r="B134" t="s">
-        <v>546</v>
+        <v>444</v>
       </c>
       <c r="C134">
-        <v>-500000</v>
+        <v>-68.099999999999994</v>
       </c>
       <c r="D134" t="s">
-        <v>349</v>
+        <v>583</v>
       </c>
       <c r="E134">
         <v>1</v>
       </c>
       <c r="F134" t="s">
-        <v>299</v>
+        <v>211</v>
       </c>
       <c r="G134" t="b">
         <v>0</v>
       </c>
       <c r="H134" t="s">
-        <v>641</v>
+        <v>598</v>
       </c>
       <c r="I134" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="J134" t="s">
-        <v>367</v>
+        <v>349</v>
       </c>
       <c r="K134" t="s">
         <v>686</v>
       </c>
       <c r="L134" t="s">
-        <v>716</v>
+        <v>689</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>125</v>
+        <v>9</v>
       </c>
       <c r="B135" t="s">
-        <v>545</v>
+        <v>447</v>
       </c>
       <c r="C135">
-        <v>-500000</v>
+        <v>-34.1</v>
       </c>
       <c r="D135" t="s">
-        <v>349</v>
+        <v>583</v>
       </c>
       <c r="E135">
         <v>1</v>
       </c>
       <c r="F135" t="s">
-        <v>299</v>
+        <v>214</v>
       </c>
       <c r="G135" t="b">
         <v>0</v>
       </c>
       <c r="H135" t="s">
-        <v>641</v>
+        <v>600</v>
       </c>
       <c r="I135" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="J135" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="K135" t="s">
         <v>686</v>
       </c>
       <c r="L135" t="s">
-        <v>716</v>
+        <v>689</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>124</v>
+        <v>11</v>
       </c>
       <c r="B136" t="s">
-        <v>544</v>
+        <v>449</v>
       </c>
       <c r="C136">
-        <v>-500000</v>
+        <v>0</v>
       </c>
       <c r="D136" t="s">
-        <v>349</v>
+        <v>583</v>
       </c>
       <c r="E136">
         <v>1</v>
       </c>
       <c r="F136" t="s">
-        <v>299</v>
+        <v>216</v>
       </c>
       <c r="G136" t="b">
         <v>0</v>
       </c>
       <c r="H136" t="s">
-        <v>641</v>
+        <v>349</v>
       </c>
       <c r="I136" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="J136" t="s">
-        <v>366</v>
+        <v>349</v>
       </c>
       <c r="K136" t="s">
         <v>686</v>
       </c>
       <c r="L136" t="s">
-        <v>716</v>
+        <v>689</v>
       </c>
     </row>
     <row r="137" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A137" t="s">
-        <v>123</v>
-      </c>
-      <c r="B137" t="s">
-        <v>543</v>
-      </c>
-      <c r="C137">
-        <v>-500000</v>
-      </c>
-      <c r="D137" t="s">
+      <c r="A137" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="C137" s="3">
+        <v>-66.2</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="E137" s="3">
+        <v>1</v>
+      </c>
+      <c r="F137" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="G137" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H137" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="I137" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="J137" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="E137">
-        <v>1</v>
-      </c>
-      <c r="F137" t="s">
-        <v>299</v>
-      </c>
-      <c r="G137" t="b">
-        <v>0</v>
-      </c>
-      <c r="H137" t="s">
-        <v>641</v>
-      </c>
-      <c r="I137" t="s">
-        <v>379</v>
-      </c>
-      <c r="J137" t="s">
-        <v>365</v>
-      </c>
-      <c r="K137" t="s">
+      <c r="K137" s="3" t="s">
         <v>686</v>
       </c>
-      <c r="L137" t="s">
-        <v>716</v>
+      <c r="L137" s="3" t="s">
+        <v>689</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>122</v>
+        <v>10</v>
       </c>
       <c r="B138" t="s">
-        <v>542</v>
+        <v>448</v>
       </c>
       <c r="C138">
-        <v>-500000</v>
+        <v>-66.2</v>
       </c>
       <c r="D138" t="s">
-        <v>349</v>
+        <v>583</v>
       </c>
       <c r="E138">
         <v>1</v>
       </c>
       <c r="F138" t="s">
-        <v>299</v>
+        <v>215</v>
       </c>
       <c r="G138" t="b">
         <v>0</v>
       </c>
       <c r="H138" t="s">
-        <v>641</v>
+        <v>601</v>
       </c>
       <c r="I138" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="J138" t="s">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="K138" t="s">
         <v>686</v>
       </c>
       <c r="L138" t="s">
-        <v>716</v>
+        <v>689</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>121</v>
+        <v>5</v>
       </c>
       <c r="B139" t="s">
-        <v>541</v>
+        <v>443</v>
       </c>
       <c r="C139">
-        <v>-500000</v>
+        <v>-6.5</v>
       </c>
       <c r="D139" t="s">
-        <v>349</v>
+        <v>583</v>
       </c>
       <c r="E139">
         <v>1</v>
       </c>
       <c r="F139" t="s">
-        <v>299</v>
+        <v>210</v>
       </c>
       <c r="G139" t="b">
         <v>0</v>
       </c>
       <c r="H139" t="s">
-        <v>641</v>
+        <v>597</v>
       </c>
       <c r="I139" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="J139" t="s">
-        <v>363</v>
+        <v>349</v>
       </c>
       <c r="K139" t="s">
         <v>686</v>
       </c>
       <c r="L139" t="s">
-        <v>716</v>
+        <v>689</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>120</v>
+        <v>8</v>
       </c>
       <c r="B140" t="s">
-        <v>540</v>
+        <v>446</v>
       </c>
       <c r="C140">
-        <v>-500000</v>
+        <v>-6.5</v>
       </c>
       <c r="D140" t="s">
-        <v>349</v>
+        <v>583</v>
       </c>
       <c r="E140">
         <v>1</v>
       </c>
       <c r="F140" t="s">
-        <v>299</v>
+        <v>213</v>
       </c>
       <c r="G140" t="b">
         <v>0</v>
       </c>
       <c r="H140" t="s">
-        <v>641</v>
+        <v>597</v>
       </c>
       <c r="I140" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="J140" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="K140" t="s">
         <v>686</v>
       </c>
       <c r="L140" t="s">
-        <v>716</v>
+        <v>689</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>119</v>
+        <v>73</v>
       </c>
       <c r="B141" t="s">
-        <v>539</v>
+        <v>467</v>
       </c>
       <c r="C141">
-        <v>-500000</v>
+        <v>-115</v>
       </c>
       <c r="D141" t="s">
+        <v>590</v>
+      </c>
+      <c r="E141">
+        <v>1</v>
+      </c>
+      <c r="F141" t="s">
+        <v>278</v>
+      </c>
+      <c r="G141" t="b">
+        <v>1</v>
+      </c>
+      <c r="H141" t="s">
+        <v>649</v>
+      </c>
+      <c r="I141" t="s">
+        <v>392</v>
+      </c>
+      <c r="J141" t="s">
         <v>349</v>
       </c>
-      <c r="E141">
-        <v>1</v>
-      </c>
-      <c r="F141" t="s">
-        <v>299</v>
-      </c>
-      <c r="G141" t="b">
-        <v>0</v>
-      </c>
-      <c r="H141" t="s">
-        <v>641</v>
-      </c>
-      <c r="I141" t="s">
-        <v>379</v>
-      </c>
-      <c r="J141" t="s">
-        <v>361</v>
-      </c>
       <c r="K141" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L141" t="s">
-        <v>716</v>
+        <v>703</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="B142" t="s">
-        <v>538</v>
+        <v>517</v>
       </c>
       <c r="C142">
-        <v>-500000</v>
+        <v>323.52941179999999</v>
       </c>
       <c r="D142" t="s">
+        <v>595</v>
+      </c>
+      <c r="E142">
+        <v>1</v>
+      </c>
+      <c r="F142" t="s">
+        <v>280</v>
+      </c>
+      <c r="G142" t="b">
+        <v>1</v>
+      </c>
+      <c r="H142" t="s">
+        <v>653</v>
+      </c>
+      <c r="I142" t="s">
+        <v>394</v>
+      </c>
+      <c r="J142" t="s">
         <v>349</v>
       </c>
-      <c r="E142">
-        <v>1</v>
-      </c>
-      <c r="F142" t="s">
-        <v>299</v>
-      </c>
-      <c r="G142" t="b">
-        <v>0</v>
-      </c>
-      <c r="H142" t="s">
-        <v>641</v>
-      </c>
-      <c r="I142" t="s">
-        <v>379</v>
-      </c>
-      <c r="J142" t="s">
-        <v>360</v>
-      </c>
       <c r="K142" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L142" t="s">
-        <v>716</v>
+        <v>706</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="B143" t="s">
-        <v>537</v>
+        <v>518</v>
       </c>
       <c r="C143">
-        <v>-500000</v>
+        <v>323.52941179999999</v>
       </c>
       <c r="D143" t="s">
+        <v>595</v>
+      </c>
+      <c r="E143">
+        <v>1</v>
+      </c>
+      <c r="F143" t="s">
+        <v>281</v>
+      </c>
+      <c r="G143" t="b">
+        <v>1</v>
+      </c>
+      <c r="H143" t="s">
+        <v>653</v>
+      </c>
+      <c r="I143" t="s">
+        <v>394</v>
+      </c>
+      <c r="J143" t="s">
         <v>349</v>
       </c>
-      <c r="E143">
-        <v>1</v>
-      </c>
-      <c r="F143" t="s">
-        <v>299</v>
-      </c>
-      <c r="G143" t="b">
-        <v>0</v>
-      </c>
-      <c r="H143" t="s">
-        <v>641</v>
-      </c>
-      <c r="I143" t="s">
-        <v>379</v>
-      </c>
-      <c r="J143" t="s">
-        <v>359</v>
-      </c>
       <c r="K143" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L143" t="s">
-        <v>716</v>
+        <v>706</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="B144" t="s">
-        <v>536</v>
+        <v>463</v>
       </c>
       <c r="C144">
-        <v>-500000</v>
+        <v>-86</v>
       </c>
       <c r="D144" t="s">
+        <v>587</v>
+      </c>
+      <c r="E144">
+        <v>1</v>
+      </c>
+      <c r="F144" t="s">
+        <v>286</v>
+      </c>
+      <c r="G144" t="b">
+        <v>1</v>
+      </c>
+      <c r="H144" t="s">
+        <v>661</v>
+      </c>
+      <c r="I144" t="s">
+        <v>397</v>
+      </c>
+      <c r="J144" t="s">
         <v>349</v>
       </c>
-      <c r="E144">
-        <v>1</v>
-      </c>
-      <c r="F144" t="s">
-        <v>299</v>
-      </c>
-      <c r="G144" t="b">
-        <v>0</v>
-      </c>
-      <c r="H144" t="s">
-        <v>641</v>
-      </c>
-      <c r="I144" t="s">
-        <v>379</v>
-      </c>
-      <c r="J144" t="s">
-        <v>358</v>
-      </c>
       <c r="K144" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L144" t="s">
-        <v>716</v>
+        <v>709</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B145" t="s">
-        <v>499</v>
+        <v>464</v>
       </c>
       <c r="C145">
-        <v>-500000</v>
+        <v>-86</v>
       </c>
       <c r="D145" t="s">
+        <v>587</v>
+      </c>
+      <c r="E145">
+        <v>1</v>
+      </c>
+      <c r="F145" t="s">
+        <v>287</v>
+      </c>
+      <c r="G145" t="b">
+        <v>1</v>
+      </c>
+      <c r="H145" t="s">
+        <v>661</v>
+      </c>
+      <c r="I145" t="s">
+        <v>397</v>
+      </c>
+      <c r="J145" t="s">
         <v>349</v>
-      </c>
-      <c r="E145">
-        <v>1</v>
-      </c>
-      <c r="F145" t="s">
-        <v>266</v>
-      </c>
-      <c r="G145" t="b">
-        <v>1</v>
-      </c>
-      <c r="H145" t="s">
-        <v>641</v>
-      </c>
-      <c r="I145" t="s">
-        <v>389</v>
-      </c>
-      <c r="J145" t="s">
-        <v>350</v>
       </c>
       <c r="K145" t="s">
         <v>687</v>
       </c>
       <c r="L145" t="s">
-        <v>700</v>
+        <v>709</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="B146" t="s">
-        <v>512</v>
+        <v>465</v>
       </c>
       <c r="C146">
-        <v>-1000000</v>
+        <v>-86</v>
       </c>
       <c r="D146" t="s">
+        <v>587</v>
+      </c>
+      <c r="E146">
+        <v>1</v>
+      </c>
+      <c r="F146" t="s">
+        <v>288</v>
+      </c>
+      <c r="G146" t="b">
+        <v>1</v>
+      </c>
+      <c r="H146" t="s">
+        <v>661</v>
+      </c>
+      <c r="I146" t="s">
+        <v>397</v>
+      </c>
+      <c r="J146" t="s">
         <v>349</v>
       </c>
-      <c r="E146">
-        <v>1</v>
-      </c>
-      <c r="F146" t="s">
-        <v>266</v>
-      </c>
-      <c r="G146" t="b">
-        <v>1</v>
-      </c>
-      <c r="H146" t="s">
-        <v>349</v>
-      </c>
-      <c r="I146" t="s">
-        <v>393</v>
-      </c>
-      <c r="J146" t="s">
-        <v>350</v>
-      </c>
       <c r="K146" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L146" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>58</v>
-      </c>
-      <c r="B147" s="3" t="s">
-        <v>497</v>
-      </c>
-      <c r="C147" s="3">
-        <v>600</v>
+        <v>95</v>
+      </c>
+      <c r="B147" t="s">
+        <v>466</v>
+      </c>
+      <c r="C147">
+        <v>-86</v>
       </c>
       <c r="D147" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="E147">
         <v>1</v>
       </c>
       <c r="F147" t="s">
-        <v>264</v>
+        <v>289</v>
       </c>
       <c r="G147" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H147" t="s">
-        <v>638</v>
+        <v>661</v>
       </c>
       <c r="I147" t="s">
-        <v>678</v>
+        <v>397</v>
       </c>
       <c r="J147" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="K147" t="s">
         <v>687</v>
       </c>
       <c r="L147" t="s">
-        <v>698</v>
+        <v>709</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>57</v>
-      </c>
-      <c r="B148" s="3" t="s">
-        <v>496</v>
-      </c>
-      <c r="C148" s="3">
-        <v>400</v>
+        <v>96</v>
+      </c>
+      <c r="B148" t="s">
+        <v>467</v>
+      </c>
+      <c r="C148">
+        <v>-60.2</v>
       </c>
       <c r="D148" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="E148">
         <v>1</v>
       </c>
       <c r="F148" t="s">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="G148" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H148" t="s">
-        <v>637</v>
+        <v>661</v>
       </c>
       <c r="I148" t="s">
-        <v>678</v>
+        <v>397</v>
       </c>
       <c r="J148" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="K148" t="s">
         <v>687</v>
       </c>
       <c r="L148" t="s">
-        <v>698</v>
+        <v>709</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>56</v>
-      </c>
-      <c r="B149" s="3" t="s">
-        <v>495</v>
-      </c>
-      <c r="C149" s="3">
-        <v>0</v>
+        <v>97</v>
+      </c>
+      <c r="B149" t="s">
+        <v>468</v>
+      </c>
+      <c r="C149">
+        <v>-60.2</v>
       </c>
       <c r="D149" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="E149">
         <v>1</v>
       </c>
       <c r="F149" t="s">
-        <v>262</v>
+        <v>291</v>
       </c>
       <c r="G149" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H149" t="s">
-        <v>636</v>
+        <v>661</v>
       </c>
       <c r="I149" t="s">
-        <v>678</v>
+        <v>397</v>
       </c>
       <c r="J149" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="K149" t="s">
         <v>687</v>
       </c>
       <c r="L149" t="s">
-        <v>698</v>
+        <v>709</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>55</v>
-      </c>
-      <c r="B150" s="3" t="s">
-        <v>494</v>
-      </c>
-      <c r="C150" s="3">
-        <v>0</v>
+        <v>24</v>
+      </c>
+      <c r="B150" t="s">
+        <v>463</v>
+      </c>
+      <c r="C150">
+        <v>-86</v>
       </c>
       <c r="D150" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="E150">
         <v>1</v>
       </c>
       <c r="F150" t="s">
-        <v>261</v>
+        <v>230</v>
       </c>
       <c r="G150" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H150" t="s">
-        <v>635</v>
+        <v>612</v>
       </c>
       <c r="I150" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="J150" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="K150" t="s">
         <v>687</v>
       </c>
       <c r="L150" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>54</v>
-      </c>
-      <c r="B151" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="C151" s="3">
-        <v>800</v>
+        <v>25</v>
+      </c>
+      <c r="B151" t="s">
+        <v>464</v>
+      </c>
+      <c r="C151">
+        <v>-61</v>
       </c>
       <c r="D151" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="E151">
         <v>1</v>
       </c>
       <c r="F151" t="s">
-        <v>260</v>
+        <v>231</v>
       </c>
       <c r="G151" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H151" t="s">
-        <v>634</v>
+        <v>613</v>
       </c>
       <c r="I151" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="J151" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="K151" t="s">
         <v>687</v>
       </c>
       <c r="L151" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>53</v>
-      </c>
-      <c r="B152" s="3" t="s">
-        <v>492</v>
-      </c>
-      <c r="C152" s="3">
-        <v>550</v>
+        <v>26</v>
+      </c>
+      <c r="B152" t="s">
+        <v>465</v>
+      </c>
+      <c r="C152">
+        <v>-70</v>
       </c>
       <c r="D152" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="E152">
         <v>1</v>
       </c>
       <c r="F152" t="s">
-        <v>259</v>
+        <v>232</v>
       </c>
       <c r="G152" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H152" t="s">
-        <v>629</v>
+        <v>614</v>
       </c>
       <c r="I152" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="J152" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="K152" t="s">
         <v>687</v>
       </c>
       <c r="L152" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>52</v>
-      </c>
-      <c r="B153" s="3" t="s">
-        <v>491</v>
-      </c>
-      <c r="C153" s="3">
-        <v>500</v>
+        <v>27</v>
+      </c>
+      <c r="B153" t="s">
+        <v>466</v>
+      </c>
+      <c r="C153">
+        <v>-57</v>
       </c>
       <c r="D153" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="E153">
         <v>1</v>
       </c>
       <c r="F153" t="s">
-        <v>258</v>
+        <v>233</v>
       </c>
       <c r="G153" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H153" t="s">
-        <v>629</v>
+        <v>615</v>
       </c>
       <c r="I153" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="J153" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="K153" t="s">
         <v>687</v>
       </c>
       <c r="L153" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>51</v>
-      </c>
-      <c r="B154" s="3" t="s">
-        <v>490</v>
-      </c>
-      <c r="C154" s="3">
-        <v>900</v>
+        <v>28</v>
+      </c>
+      <c r="B154" t="s">
+        <v>467</v>
+      </c>
+      <c r="C154">
+        <v>-7</v>
       </c>
       <c r="D154" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="E154">
         <v>1</v>
       </c>
       <c r="F154" t="s">
-        <v>257</v>
+        <v>234</v>
       </c>
       <c r="G154" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H154" t="s">
-        <v>633</v>
+        <v>616</v>
       </c>
       <c r="I154" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="J154" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="K154" t="s">
         <v>687</v>
       </c>
       <c r="L154" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>50</v>
-      </c>
-      <c r="B155" s="3" t="s">
-        <v>489</v>
-      </c>
-      <c r="C155" s="3">
-        <v>600</v>
+        <v>29</v>
+      </c>
+      <c r="B155" t="s">
+        <v>468</v>
+      </c>
+      <c r="C155">
+        <v>-72</v>
       </c>
       <c r="D155" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="E155">
         <v>1</v>
       </c>
       <c r="F155" t="s">
-        <v>256</v>
+        <v>235</v>
       </c>
       <c r="G155" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H155" t="s">
-        <v>629</v>
+        <v>617</v>
       </c>
       <c r="I155" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="J155" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="K155" t="s">
         <v>687</v>
       </c>
       <c r="L155" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A156" t="s">
-        <v>49</v>
-      </c>
-      <c r="B156" s="3" t="s">
-        <v>488</v>
-      </c>
-      <c r="C156" s="3">
-        <v>500</v>
+      <c r="A156" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B156" s="11" t="s">
+        <v>517</v>
+      </c>
+      <c r="C156" s="11">
+        <f>-500/3</f>
+        <v>-166.66666666666666</v>
       </c>
       <c r="D156" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="E156">
         <v>1</v>
       </c>
       <c r="F156" t="s">
-        <v>255</v>
+        <v>280</v>
       </c>
       <c r="G156" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H156" t="s">
-        <v>632</v>
+        <v>653</v>
       </c>
       <c r="I156" t="s">
-        <v>678</v>
+        <v>394</v>
       </c>
       <c r="J156" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="K156" t="s">
         <v>687</v>
       </c>
       <c r="L156" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A157" t="s">
-        <v>48</v>
-      </c>
-      <c r="B157" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="C157" s="3">
-        <v>500</v>
+      <c r="A157" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="B157" s="11" t="s">
+        <v>516</v>
+      </c>
+      <c r="C157" s="11">
+        <f>-170/3</f>
+        <v>-56.666666666666664</v>
       </c>
       <c r="D157" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="E157">
         <v>1</v>
       </c>
       <c r="F157" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="G157" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H157" t="s">
-        <v>631</v>
+        <v>652</v>
       </c>
       <c r="I157" t="s">
-        <v>678</v>
+        <v>394</v>
       </c>
       <c r="J157" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="K157" t="s">
         <v>687</v>
       </c>
       <c r="L157" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A158" t="s">
-        <v>47</v>
-      </c>
-      <c r="B158" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="C158" s="3">
-        <v>350</v>
+      <c r="A158" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B158" s="11" t="s">
+        <v>518</v>
+      </c>
+      <c r="C158" s="11">
+        <f>-500/3</f>
+        <v>-166.66666666666666</v>
       </c>
       <c r="D158" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="E158">
         <v>1</v>
       </c>
       <c r="F158" t="s">
-        <v>253</v>
+        <v>281</v>
       </c>
       <c r="G158" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H158" t="s">
-        <v>630</v>
+        <v>653</v>
       </c>
       <c r="I158" t="s">
-        <v>678</v>
-      </c>
-      <c r="J158" t="s">
-        <v>352</v>
+        <v>394</v>
+      </c>
+      <c r="J158" s="2" t="s">
+        <v>356</v>
       </c>
       <c r="K158" t="s">
         <v>687</v>
       </c>
       <c r="L158" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>46</v>
-      </c>
-      <c r="B159" s="3" t="s">
-        <v>485</v>
-      </c>
-      <c r="C159" s="3">
-        <v>400</v>
+        <v>14</v>
+      </c>
+      <c r="B159" t="s">
+        <v>453</v>
+      </c>
+      <c r="C159">
+        <v>1</v>
       </c>
       <c r="D159" t="s">
-        <v>590</v>
+        <v>349</v>
       </c>
       <c r="E159">
         <v>1</v>
       </c>
       <c r="F159" t="s">
-        <v>252</v>
+        <v>220</v>
       </c>
       <c r="G159" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H159" t="s">
-        <v>629</v>
+        <v>349</v>
       </c>
       <c r="I159" t="s">
-        <v>678</v>
+        <v>349</v>
       </c>
       <c r="J159" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="K159" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L159" t="s">
-        <v>698</v>
+        <v>691</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L159" xr:uid="{00000000-0001-0000-0100-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L159">
-      <sortCondition descending="1" ref="A1:A159"/>
+      <sortCondition ref="A1:A159"/>
     </sortState>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="J3" r:id="rId1" location=":~:text=Using%20the%20World%20Bank%20numbers,case%20of%20U.S.%20LMOP%20landfills." xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="J158" r:id="rId1" location=":~:text=Using%20the%20World%20Bank%20numbers,case%20of%20U.S.%20LMOP%20landfills." xr:uid="{A2EFEDF8-FD3C-7245-8EF7-7050BD8DEE09}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -23430,7 +23426,7 @@
         <v>451</v>
       </c>
       <c r="I10">
-        <v>1000000</v>
+        <v>-1000000</v>
       </c>
       <c r="J10" t="s">
         <v>349</v>

--- a/ssp_modeling/cost-benefits/cb_config_files/cb_config_params.xlsx
+++ b/ssp_modeling/cost-benefits/cb_config_files/cb_config_params.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_libya/ssp_modeling/cost-benefits/cb_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C1D6B1C-A49E-194A-87C3-A1A74D737826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E983885F-56E9-9443-8F64-44D05069125E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38460" yWindow="-7160" windowWidth="30240" windowHeight="18980" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tx_table" sheetId="1" r:id="rId1"/>
@@ -33,8 +33,22 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">cost_factors!$A$1:$L$159</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">transformation_costs!$A$1:$O$56</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -6294,12 +6308,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -6329,11 +6349,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -22853,7 +22874,12 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="46.1640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="37.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
@@ -24032,34 +24058,34 @@
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
+      <c r="A26" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="2" t="s">
         <v>811</v>
       </c>
-      <c r="C26" t="b">
-        <v>1</v>
-      </c>
-      <c r="D26">
+      <c r="C26" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D26" s="2">
         <v>99</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="2" t="s">
         <v>749</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F26" s="2" t="s">
         <v>750</v>
       </c>
-      <c r="G26" t="s">
+      <c r="G26" s="2" t="s">
         <v>745</v>
       </c>
-      <c r="H26" t="s">
+      <c r="H26" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="I26">
-        <v>-88</v>
-      </c>
-      <c r="J26" t="s">
+      <c r="I26" s="2">
+        <v>-400</v>
+      </c>
+      <c r="J26" s="2" t="s">
         <v>588</v>
       </c>
       <c r="K26">
@@ -25489,6 +25515,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:O56" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/ssp_modeling/cost-benefits/cb_config_files/cb_config_params.xlsx
+++ b/ssp_modeling/cost-benefits/cb_config_files/cb_config_params.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_libya/ssp_modeling/cost-benefits/cb_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E983885F-56E9-9443-8F64-44D05069125E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD0C10AF-1290-144B-A860-047B9CF246BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-51200" yWindow="-7160" windowWidth="37140" windowHeight="25280" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tx_table" sheetId="1" r:id="rId1"/>
@@ -25493,7 +25493,8 @@
         <v>777</v>
       </c>
       <c r="I56">
-        <v>-8500000</v>
+        <f>-22*1000000</f>
+        <v>-22000000</v>
       </c>
       <c r="J56" t="s">
         <v>778</v>
